--- a/excel/quick_commerce_model.xlsx
+++ b/excel/quick_commerce_model.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Per-order P&amp;L" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Store daily P&amp;L" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Break-even" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Lever ranking" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="264">
   <si>
     <t xml:space="preserve">Assumptions: synthetic quick-commerce dark store, calibrated to Swiggy Instamart Q2 FY27 (quarter ended 30-Sep-2026)</t>
   </si>
@@ -396,7 +399,82 @@
     <t xml:space="preserve">Blinkit orders per store per day (derived: 902k NOV per store per day / 525)</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Model checks</t>
+    <t xml:space="preserve">8. Day 3 settings (table axes and ranking step; edit to change the tables)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order value axis: first point (change vs base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity table axis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order value axis: step between points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per day axis: first point (change vs base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per day axis: step between points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost axis: first point (change vs base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost axis: step between points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size of the favourable change used to rank the levers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roadmap: rank levers for a 10% change in each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Day 3 building blocks at the base case (formulas; ignore the scenario levers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin on each rupee of NOV after payment costs (product margin % less payment cost %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other per-order items except delivery (ad income + customer fees - discounts - picking and packing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark store fixed cost per order at base volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM2 per order at base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store contribution per order at base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store contribution per day at base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Model checks</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue split residual is not negative</t>
@@ -414,6 +492,15 @@
     <t xml:space="preserve">Store daily P&amp;L ties to per-order P&amp;L</t>
   </si>
   <si>
+    <t xml:space="preserve">Day 3 building blocks equal the reported derived contribution per order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution at the break-even volume is zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lever ranking base equals Store daily P&amp;L (only when all levers are 0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Per-order P&amp;L (INR per order)</t>
   </si>
   <si>
@@ -589,19 +676,163 @@
   </si>
   <si>
     <t xml:space="preserve">Difference vs Per-order P&amp;L (should be 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even (store level, INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All figures start from the base case on the Assumptions sheet and ignore the scenario levers. Modeled scenario estimates for a synthetic store, not company measurements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Break-even orders per store per day (everything else at base case)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INR/order: what each extra order contributes toward fixed cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even orders per store per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed cost per day / CM2 per order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base orders per store per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instamart Q2 FY27, reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra orders needed per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase needed in orders per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: Blinkit orders per store per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived from Eternal's NOV per store per day / NAOV; not a reported figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even volume less Blinkit reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative = break-even volume is below what Blinkit stores already do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Break-even by single lever (one lever moves, all others stay at base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order value (NOV per order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost per order (needs to fall)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ad income per order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to read: the store loses money per order at base. Each row shows how far that single lever alone would have to move to reach zero store contribution. Levers can be combined, which needs smaller moves in each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity tables: store contribution per day (INR per store per day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base case on the Assumptions sheet, scenario levers ignored. Green = store profit, red = store loss. Modeled scenario estimates for a synthetic store, not company measurements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Order value x orders per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order value change (down) / orders per day change (across)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOV, INR/order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 2. Delivery cost x order value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost change (down) / order value change (across)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost, INR/order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lever ranking: effect of a favourable change in each lever (INR per store per day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One lever changes at a time, all others at base. Ranks profit impact only, not how easy each change would be. Modeled scenario estimates, not company measurements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size of favourable change applied to each lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base store contribution per day (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store contribution per day after change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change vs base, INR/day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of base daily loss closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution per order after change, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order value up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per day up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost per order down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ad income per order up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranked, largest profit impact first</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.00%"/>
+    <numFmt numFmtId="170" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="171" formatCode="\+0.0%;\-0.0%;0.0%"/>
+    <numFmt numFmtId="172" formatCode="0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -778,7 +1009,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -867,6 +1098,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -887,7 +1122,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -899,7 +1134,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -929,6 +1164,70 @@
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -940,6 +1239,36 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF9C0006"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006100"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -950,7 +1279,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -976,12 +1305,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -992,7 +1321,7 @@
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
@@ -1183,7 +1512,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -2219,72 +2548,415 @@
       <c r="H54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
+      <c r="A55" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="B55" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="22" t="str">
+        <v>126</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="14"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="14"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="14"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="14"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="14"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="14"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="14"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5"/>
+      <c r="B63" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" s="22" t="n">
+        <f aca="false">$C$37-$C$43</f>
+        <v>0.101962330772101</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="14"/>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5"/>
+      <c r="B64" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C64" s="18" t="n">
+        <f aca="false">$C$38+$C$39-$C$40-$C$42</f>
+        <v>11.1273215656178</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="14"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5"/>
+      <c r="B65" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="18" t="n">
+        <f aca="false">$C$44/$C$10</f>
+        <v>26.8476592478895</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="14"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5"/>
+      <c r="B66" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" s="18" t="n">
+        <f aca="false">$C$63*$C$9+$C$64-$C$41</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="14"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5"/>
+      <c r="B67" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C67" s="18" t="n">
+        <f aca="false">$C$66-$C$65</f>
+        <v>-7.08365310821181</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="14"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5"/>
+      <c r="B68" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C68" s="21" t="n">
+        <f aca="false">$C$67*$C$10</f>
+        <v>-8443.71450498848</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="14"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5"/>
+      <c r="B70" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" s="23" t="str">
         <f aca="false">IF($C$24&gt;=0,"OK","CHECK")</f>
         <v>OK</v>
       </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="14"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="B56" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="22" t="str">
+      <c r="D70" s="5"/>
+      <c r="E70" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="14"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5"/>
+      <c r="B71" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" s="23" t="str">
         <f aca="false">IF($C$29&gt;=0,"OK","CHECK")</f>
         <v>OK</v>
       </c>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="14"/>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5"/>
-      <c r="B57" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="22" t="str">
+      <c r="D71" s="5"/>
+      <c r="E71" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F71" s="12"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="14"/>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5"/>
+      <c r="B72" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" s="23" t="str">
         <f aca="false">IF(ABS($C$32)+ABS($C$33)+ABS($C$34)+ABS($C$35)&gt;0,"Levers on: n/a",IF(ABS('Per-order P&amp;L'!$B$19-$C$19)&lt;0.000001,"OK","CHECK"))</f>
         <v>OK</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="14"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
-      <c r="B58" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="22" t="str">
+      <c r="D72" s="5"/>
+      <c r="E72" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F72" s="12"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="14"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5"/>
+      <c r="B73" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="23" t="str">
         <f aca="false">IF(ABS('Store daily P&amp;L'!$B$19/'Store daily P&amp;L'!$B$4-'Per-order P&amp;L'!$B$19)&lt;0.000001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="14"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F73" s="12"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="14"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5"/>
+      <c r="B74" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" s="23" t="str">
+        <f aca="false">IF(ABS($C$67-$C$19)&lt;0.000001,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="14"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5"/>
+      <c r="B75" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" s="23" t="str">
+        <f aca="false">IF(ISNUMBER('Break-even'!$B$8),IF(ABS('Break-even'!$B$8*'Break-even'!$B$7-'Break-even'!$B$6)&lt;0.001,"OK","CHECK"),"n/a")</f>
+        <v>OK</v>
+      </c>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="14"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5"/>
+      <c r="B76" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="23" t="str">
+        <f aca="false">IF(ABS($C$32)+ABS($C$33)+ABS($C$34)+ABS($C$35)&gt;0,"Levers on: n/a",IF(ABS('Lever ranking'!$B$5-'Store daily P&amp;L'!$B$19)&lt;0.001,"OK","CHECK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2316,308 +2988,308 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="A3" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="A5" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>135</v>
+      <c r="D5" s="25" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="26" t="n">
+      <c r="A6" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="27" t="n">
         <f aca="false">Assumptions!$C$46</f>
         <v>506</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <f aca="false">IF($B$6=0,0,B6/$B$6)</f>
         <v>1</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>137</v>
+      <c r="D6" s="29" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="29" t="n">
+        <v>166</v>
+      </c>
+      <c r="B7" s="30" t="n">
         <f aca="false">-B6*(1-Assumptions!$C$37)</f>
         <v>-445.815809669992</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B7/$B$6)</f>
         <v>-0.881058912391289</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>139</v>
+      <c r="D7" s="32" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="29" t="n">
+        <v>168</v>
+      </c>
+      <c r="B8" s="30" t="n">
         <f aca="false">B6+B7</f>
         <v>60.1841903300077</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B8/$B$6)</f>
         <v>0.118941087608711</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>141</v>
+      <c r="D8" s="32" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" s="32" t="n">
+        <v>170</v>
+      </c>
+      <c r="B9" s="33" t="n">
         <f aca="false">Assumptions!$C$49</f>
         <v>20.0613967766692</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B9/$B$6)</f>
         <v>0.0396470292029036</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="32" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="32" t="n">
+        <v>171</v>
+      </c>
+      <c r="B10" s="33" t="n">
         <f aca="false">Assumptions!$C$39</f>
         <v>20.0613967766692</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B10/$B$6)</f>
         <v>0.0396470292029036</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="33" t="n">
+      <c r="A11" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="34" t="n">
         <f aca="false">B8+B9+B10</f>
         <v>100.306983883346</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <f aca="false">IF($B$6=0,0,B11/$B$6)</f>
         <v>0.198235146014518</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>145</v>
+      <c r="D11" s="29" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="29" t="n">
+        <v>174</v>
+      </c>
+      <c r="B12" s="30" t="n">
         <f aca="false">-Assumptions!$C$40</f>
         <v>-12.886876438987</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B12/$B$6)</f>
         <v>-0.0254681352549149</v>
       </c>
-      <c r="D12" s="31"/>
+      <c r="D12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="33" t="n">
+      <c r="A13" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="34" t="n">
         <f aca="false">B11+B12</f>
         <v>87.4201074443592</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <f aca="false">IF($B$6=0,0,B13/$B$6)</f>
         <v>0.172767010759603</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>148</v>
+      <c r="D13" s="29" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="29" t="n">
+        <v>177</v>
+      </c>
+      <c r="B14" s="30" t="n">
         <f aca="false">-Assumptions!$C$42</f>
         <v>-16.1085955487337</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B14/$B$6)</f>
         <v>-0.0318351690686437</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="29" t="n">
+        <v>178</v>
+      </c>
+      <c r="B15" s="30" t="n">
         <f aca="false">-Assumptions!$C$48</f>
         <v>-42.9562547966232</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B15/$B$6)</f>
         <v>-0.0848937841830497</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="32" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="29" t="n">
+        <v>179</v>
+      </c>
+      <c r="B16" s="30" t="n">
         <f aca="false">-B6*Assumptions!$C$43</f>
         <v>-8.59125095932463</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B16/$B$6)</f>
         <v>-0.01697875683661</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>152</v>
+      <c r="D16" s="32" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B17" s="33" t="n">
+      <c r="A17" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="34" t="n">
         <f aca="false">B13+B14+B15+B16</f>
         <v>19.7640061396777</v>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <f aca="false">IF($B$6=0,0,B17/$B$6)</f>
         <v>0.0390593006712997</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>154</v>
+      <c r="D17" s="29" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" s="29" t="n">
+        <v>183</v>
+      </c>
+      <c r="B18" s="30" t="n">
         <f aca="false">IF(Assumptions!$C$47=0,0,-Assumptions!$C$44/Assumptions!$C$47)</f>
         <v>-26.8476592478895</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="31" t="n">
         <f aca="false">IF($B$6=0,0,B18/$B$6)</f>
         <v>-0.0530586151144061</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>156</v>
+      <c r="D18" s="32" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="33" t="n">
+      <c r="A19" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="34" t="n">
         <f aca="false">B17+B18</f>
         <v>-7.08365310821181</v>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="28" t="n">
         <f aca="false">IF($B$6=0,0,B19/$B$6)</f>
         <v>-0.0139993144431063</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>158</v>
+      <c r="D19" s="29" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="32" t="n">
+        <v>188</v>
+      </c>
+      <c r="B22" s="33" t="n">
         <f aca="false">Assumptions!$C$19</f>
         <v>-7.08365310821182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B23" s="29" t="n">
+        <v>189</v>
+      </c>
+      <c r="B23" s="30" t="n">
         <f aca="false">B19-B22</f>
         <v>0</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>162</v>
+      <c r="D23" s="32" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B24" s="32" t="n">
+        <v>191</v>
+      </c>
+      <c r="B24" s="33" t="n">
         <f aca="false">Assumptions!$C$15</f>
         <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B25" s="29" t="n">
+        <v>192</v>
+      </c>
+      <c r="B25" s="30" t="n">
         <f aca="false">B19-B24</f>
         <v>-37.0836531082118</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>165</v>
+      <c r="D25" s="32" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="32" t="n">
+        <v>194</v>
+      </c>
+      <c r="B26" s="33" t="n">
         <f aca="false">Assumptions!$C$51</f>
         <v>28</v>
       </c>
@@ -2651,286 +3323,1572 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="34" t="n">
+        <v>197</v>
+      </c>
+      <c r="B4" s="35" t="n">
         <f aca="false">Assumptions!$C$47</f>
         <v>1192</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="36" t="n">
         <f aca="false">B4*Assumptions!$C$30</f>
         <v>35760</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>135</v>
+      <c r="A5" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="36" t="n">
+      <c r="A6" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B6</f>
         <v>603152</v>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="37" t="n">
         <f aca="false">B6*Assumptions!$C$30</f>
         <v>18094560</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>172</v>
+      <c r="D6" s="29" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="37" t="n">
+        <v>166</v>
+      </c>
+      <c r="B7" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B7</f>
         <v>-531412.445126631</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="38" t="n">
         <f aca="false">B7*Assumptions!$C$30</f>
         <v>-15942373.3537989</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>173</v>
+      <c r="D7" s="32" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="37" t="n">
+        <v>168</v>
+      </c>
+      <c r="B8" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B8</f>
         <v>71739.5548733691</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="38" t="n">
         <f aca="false">B8*Assumptions!$C$30</f>
         <v>2152186.64620107</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>174</v>
+      <c r="D8" s="32" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" s="37" t="n">
+        <v>170</v>
+      </c>
+      <c r="B9" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B9</f>
         <v>23913.1849577897</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="38" t="n">
         <f aca="false">B9*Assumptions!$C$30</f>
         <v>717395.548733692</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>175</v>
+      <c r="D9" s="32" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="37" t="n">
+        <v>171</v>
+      </c>
+      <c r="B10" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B10</f>
         <v>23913.1849577897</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="38" t="n">
         <f aca="false">B10*Assumptions!$C$30</f>
         <v>717395.548733692</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>176</v>
+      <c r="D10" s="32" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="36" t="n">
+      <c r="A11" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B11</f>
         <v>119565.924788949</v>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="37" t="n">
         <f aca="false">B11*Assumptions!$C$30</f>
         <v>3586977.74366846</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>177</v>
+      <c r="D11" s="29" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="37" t="n">
+        <v>174</v>
+      </c>
+      <c r="B12" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B12</f>
         <v>-15361.1567152724</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="38" t="n">
         <f aca="false">B12*Assumptions!$C$30</f>
         <v>-460834.701458173</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>178</v>
+      <c r="D12" s="32" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="36" t="n">
+      <c r="A13" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B13</f>
         <v>104204.768073676</v>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="37" t="n">
         <f aca="false">B13*Assumptions!$C$30</f>
         <v>3126143.04221028</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>179</v>
+      <c r="D13" s="29" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="37" t="n">
+        <v>177</v>
+      </c>
+      <c r="B14" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B14</f>
         <v>-19201.4458940906</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="38" t="n">
         <f aca="false">B14*Assumptions!$C$30</f>
         <v>-576043.376822717</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>180</v>
+      <c r="D14" s="32" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="37" t="n">
+        <v>178</v>
+      </c>
+      <c r="B15" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B15</f>
         <v>-51203.8557175748</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="38" t="n">
         <f aca="false">B15*Assumptions!$C$30</f>
         <v>-1536115.67152724</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>181</v>
+      <c r="D15" s="32" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="37" t="n">
+        <v>179</v>
+      </c>
+      <c r="B16" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B16</f>
         <v>-10240.771143515</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="38" t="n">
         <f aca="false">B16*Assumptions!$C$30</f>
         <v>-307223.134305449</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>182</v>
+      <c r="D16" s="32" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B17" s="36" t="n">
+      <c r="A17" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B17</f>
         <v>23558.6953184958</v>
       </c>
-      <c r="C17" s="36" t="n">
+      <c r="C17" s="37" t="n">
         <f aca="false">B17*Assumptions!$C$30</f>
         <v>706760.859554873</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>183</v>
+      <c r="D17" s="29" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B18" s="37" t="n">
+        <v>212</v>
+      </c>
+      <c r="B18" s="38" t="n">
         <f aca="false">-Assumptions!$C$44</f>
         <v>-32002.4098234843</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="38" t="n">
         <f aca="false">B18*Assumptions!$C$30</f>
         <v>-960072.294704528</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="32" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B19</f>
         <v>-8443.71450498847</v>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="37" t="n">
         <f aca="false">B19*Assumptions!$C$30</f>
         <v>-253311.435149654</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>186</v>
+      <c r="D19" s="29" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="29" t="n">
+        <v>215</v>
+      </c>
+      <c r="B22" s="30" t="n">
         <f aca="false">IF(B4=0,0,B19/B4)</f>
         <v>-7.08365310821181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" s="29" t="n">
+        <v>216</v>
+      </c>
+      <c r="B23" s="30" t="n">
         <f aca="false">B22-'Per-order P&amp;L'!B19</f>
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="41" t="n">
+        <f aca="false">Assumptions!$C$44</f>
+        <v>32002.4098234843</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="42" t="n">
+        <f aca="false">Assumptions!$C$66</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="44" t="n">
+        <f aca="false">IF(B7&lt;=0,"No break-even: CM2 is not positive",B6/B7)</f>
+        <v>1619.22687117756</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="41" t="n">
+        <f aca="false">Assumptions!$C$10</f>
+        <v>1192</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(B8),B8-B9,"n/a")</f>
+        <v>427.226871177555</v>
+      </c>
+      <c r="C10" s="32"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="45" t="n">
+        <f aca="false">IF(ISNUMBER(B8),IF(B9=0,0,B8/B9-1),"n/a")</f>
+        <v>0.358411804679157</v>
+      </c>
+      <c r="C11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="41" t="n">
+        <f aca="false">Assumptions!$C$53</f>
+        <v>1718</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(B8),B8-B12,"n/a")</f>
+        <v>-98.7731288224447</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="42" t="n">
+        <f aca="false">Assumptions!$C$9</f>
+        <v>506</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <f aca="false">IF(Assumptions!$C$63&lt;=0,"n/a",B17-Assumptions!$C$67/Assumptions!$C$63)</f>
+        <v>575.473236386139</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">IF(ISNUMBER(C17),C17-B17,"n/a")</f>
+        <v>69.4732363861385</v>
+      </c>
+      <c r="E17" s="45" t="n">
+        <f aca="false">IF(ISNUMBER(C17),IF(B17=0,0,C17/B17-1),"n/a")</f>
+        <v>0.137298886138614</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="41" t="n">
+        <f aca="false">Assumptions!$C$10</f>
+        <v>1192</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <f aca="false">B8</f>
+        <v>1619.22687117756</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <f aca="false">IF(ISNUMBER(C18),C18-B18,"n/a")</f>
+        <v>427.226871177555</v>
+      </c>
+      <c r="E18" s="45" t="n">
+        <f aca="false">IF(ISNUMBER(C18),IF(B18=0,0,C18/B18-1),"n/a")</f>
+        <v>0.358411804679157</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" s="42" t="n">
+        <f aca="false">Assumptions!$C$41</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <f aca="false">B19+Assumptions!$C$67</f>
+        <v>35.8726016884114</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">IF(ISNUMBER(C19),C19-B19,"n/a")</f>
+        <v>-7.08365310821181</v>
+      </c>
+      <c r="E19" s="45" t="n">
+        <f aca="false">IF(ISNUMBER(C19),IF(B19=0,0,C19/B19-1),"n/a")</f>
+        <v>-0.164903880511684</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B20" s="42" t="n">
+        <f aca="false">Assumptions!$C$38</f>
+        <v>20.0613967766692</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <f aca="false">B20-Assumptions!$C$67</f>
+        <v>27.145049884881</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">IF(ISNUMBER(C20),C20-B20,"n/a")</f>
+        <v>7.08365310821181</v>
+      </c>
+      <c r="E20" s="45" t="n">
+        <f aca="false">IF(ISNUMBER(C20),IF(B20=0,0,C20/B20-1),"n/a")</f>
+        <v>0.3530986993114</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <f aca="false">Assumptions!$C$57</f>
+        <v>-0.2</v>
+      </c>
+      <c r="D5" s="46" t="n">
+        <f aca="false">C5+Assumptions!$C$58</f>
+        <v>-0.1</v>
+      </c>
+      <c r="E5" s="46" t="n">
+        <f aca="false">D5+Assumptions!$C$58</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="46" t="n">
+        <f aca="false">E5+Assumptions!$C$58</f>
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <f aca="false">F5+Assumptions!$C$58</f>
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="46" t="n">
+        <f aca="false">G5+Assumptions!$C$58</f>
+        <v>0.3</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <f aca="false">H5+Assumptions!$C$58</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+C5)</f>
+        <v>953.6</v>
+      </c>
+      <c r="D6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D5)</f>
+        <v>1072.8</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+E5)</f>
+        <v>1192</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+F5)</f>
+        <v>1311.2</v>
+      </c>
+      <c r="G6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+G5)</f>
+        <v>1430.4</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+H5)</f>
+        <v>1549.6</v>
+      </c>
+      <c r="I6" s="47" t="n">
+        <f aca="false">Assumptions!$C$10*(1+I5)</f>
+        <v>1668.8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="46" t="n">
+        <f aca="false">Assumptions!$C$55</f>
+        <v>-0.1</v>
+      </c>
+      <c r="B7" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A7)</f>
+        <v>455.4</v>
+      </c>
+      <c r="C7" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-18075.356267076</v>
+      </c>
+      <c r="D7" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-16334.4745725249</v>
+      </c>
+      <c r="E7" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-14593.5928779739</v>
+      </c>
+      <c r="F7" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-12852.7111834229</v>
+      </c>
+      <c r="G7" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-11111.8294888718</v>
+      </c>
+      <c r="H7" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-9370.94779432078</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-7630.06609976975</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="n">
+        <f aca="false">A7+Assumptions!$C$56</f>
+        <v>-0.05</v>
+      </c>
+      <c r="B8" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A8)</f>
+        <v>480.7</v>
+      </c>
+      <c r="C8" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-15615.4049178818</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-13567.0293046815</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-11518.6536914812</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-9470.27807828088</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-7421.90246508058</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-5373.52685188026</v>
+      </c>
+      <c r="I8" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-3325.15123867996</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46" t="n">
+        <f aca="false">A8+Assumptions!$C$56</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A9)</f>
+        <v>506</v>
+      </c>
+      <c r="C9" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-13155.4535686876</v>
+      </c>
+      <c r="D9" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-10799.5840368381</v>
+      </c>
+      <c r="E9" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-8443.71450498848</v>
+      </c>
+      <c r="F9" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-6087.8449731389</v>
+      </c>
+      <c r="G9" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-3731.97544128933</v>
+      </c>
+      <c r="H9" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-1376.10590943975</v>
+      </c>
+      <c r="I9" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>979.763622409824</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="46" t="n">
+        <f aca="false">A9+Assumptions!$C$56</f>
+        <v>0.05</v>
+      </c>
+      <c r="B10" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A10)</f>
+        <v>531.3</v>
+      </c>
+      <c r="C10" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-10695.5022194935</v>
+      </c>
+      <c r="D10" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-8032.13876899462</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-5368.77531849578</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-2705.41186799693</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-42.0484174980811</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>2621.31503300077</v>
+      </c>
+      <c r="I10" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>5284.67848349961</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="46" t="n">
+        <f aca="false">A10+Assumptions!$C$56</f>
+        <v>0.1</v>
+      </c>
+      <c r="B11" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A11)</f>
+        <v>556.6</v>
+      </c>
+      <c r="C11" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-8235.55087029931</v>
+      </c>
+      <c r="D11" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-5264.69350115119</v>
+      </c>
+      <c r="E11" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-2293.83613200307</v>
+      </c>
+      <c r="F11" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>677.021237145051</v>
+      </c>
+      <c r="G11" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>3647.87860629316</v>
+      </c>
+      <c r="H11" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>6618.73597544129</v>
+      </c>
+      <c r="I11" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>9589.5933445894</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="46" t="n">
+        <f aca="false">A11+Assumptions!$C$56</f>
+        <v>0.15</v>
+      </c>
+      <c r="B12" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A12)</f>
+        <v>581.9</v>
+      </c>
+      <c r="C12" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-5775.59952110514</v>
+      </c>
+      <c r="D12" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-2497.24823330775</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>781.103054489635</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>4059.45434228703</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>7337.80563008441</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>10616.1569178818</v>
+      </c>
+      <c r="I12" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>13894.5082056792</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="46" t="n">
+        <f aca="false">A12+Assumptions!$C$56</f>
+        <v>0.2</v>
+      </c>
+      <c r="B13" s="48" t="n">
+        <f aca="false">Assumptions!$C$9*(1+A13)</f>
+        <v>607.2</v>
+      </c>
+      <c r="C13" s="38" t="n">
+        <f aca="false">C$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-3315.64817191098</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <f aca="false">D$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>270.197034535682</v>
+      </c>
+      <c r="E13" s="38" t="n">
+        <f aca="false">E$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>3856.04224098234</v>
+      </c>
+      <c r="F13" s="38" t="n">
+        <f aca="false">F$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>7441.88744742901</v>
+      </c>
+      <c r="G13" s="38" t="n">
+        <f aca="false">G$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>11027.7326538757</v>
+      </c>
+      <c r="H13" s="38" t="n">
+        <f aca="false">H$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>14613.5778603223</v>
+      </c>
+      <c r="I13" s="38" t="n">
+        <f aca="false">I$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>18199.423066769</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="46" t="n">
+        <f aca="false">Assumptions!$C$55</f>
+        <v>-0.1</v>
+      </c>
+      <c r="D17" s="46" t="n">
+        <f aca="false">C17+Assumptions!$C$56</f>
+        <v>-0.05</v>
+      </c>
+      <c r="E17" s="46" t="n">
+        <f aca="false">D17+Assumptions!$C$56</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <f aca="false">E17+Assumptions!$C$56</f>
+        <v>0.05</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <f aca="false">F17+Assumptions!$C$56</f>
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="46" t="n">
+        <f aca="false">G17+Assumptions!$C$56</f>
+        <v>0.15</v>
+      </c>
+      <c r="I17" s="46" t="n">
+        <f aca="false">H17+Assumptions!$C$56</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C17)</f>
+        <v>455.4</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+D17)</f>
+        <v>480.7</v>
+      </c>
+      <c r="E18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+E17)</f>
+        <v>506</v>
+      </c>
+      <c r="F18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+F17)</f>
+        <v>531.3</v>
+      </c>
+      <c r="G18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+G17)</f>
+        <v>556.6</v>
+      </c>
+      <c r="H18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+H17)</f>
+        <v>581.9</v>
+      </c>
+      <c r="I18" s="49" t="n">
+        <f aca="false">Assumptions!$C$9*(1+I17)</f>
+        <v>607.2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="46" t="n">
+        <f aca="false">Assumptions!$C$59</f>
+        <v>-0.3</v>
+      </c>
+      <c r="B19" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A19)</f>
+        <v>30.0693783576362</v>
+      </c>
+      <c r="C19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>767.563837298556</v>
+      </c>
+      <c r="D19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>3842.50302379126</v>
+      </c>
+      <c r="E19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>6917.44221028397</v>
+      </c>
+      <c r="F19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>9992.38139677668</v>
+      </c>
+      <c r="G19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>13067.3205832694</v>
+      </c>
+      <c r="H19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>16142.2597697621</v>
+      </c>
+      <c r="I19" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <v>19217.1989562548</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="46" t="n">
+        <f aca="false">A19+Assumptions!$C$60</f>
+        <v>-0.2</v>
+      </c>
+      <c r="B20" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A20)</f>
+        <v>34.3650038372985</v>
+      </c>
+      <c r="C20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>-4352.82173445893</v>
+      </c>
+      <c r="D20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>-1277.88254796622</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>1797.05663852648</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>4871.99582501919</v>
+      </c>
+      <c r="G20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>7946.93501151189</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>11021.8741980046</v>
+      </c>
+      <c r="I20" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <v>14096.8133844973</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="46" t="n">
+        <f aca="false">A20+Assumptions!$C$60</f>
+        <v>-0.1</v>
+      </c>
+      <c r="B21" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A21)</f>
+        <v>38.6606293169609</v>
+      </c>
+      <c r="C21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>-9473.20730621642</v>
+      </c>
+      <c r="D21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>-6398.26811972371</v>
+      </c>
+      <c r="E21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>-3323.32893323101</v>
+      </c>
+      <c r="F21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>-248.389746738299</v>
+      </c>
+      <c r="G21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>2826.54943975441</v>
+      </c>
+      <c r="H21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>5901.48862624711</v>
+      </c>
+      <c r="I21" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <v>8976.42781273982</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="46" t="n">
+        <f aca="false">A21+Assumptions!$C$60</f>
+        <v>0</v>
+      </c>
+      <c r="B22" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A22)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="C22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>-14593.5928779739</v>
+      </c>
+      <c r="D22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>-11518.6536914812</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>-8443.71450498848</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>-5368.77531849578</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>-2293.83613200307</v>
+      </c>
+      <c r="H22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>781.103054489635</v>
+      </c>
+      <c r="I22" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <v>3856.04224098234</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="46" t="n">
+        <f aca="false">A22+Assumptions!$C$60</f>
+        <v>0.1</v>
+      </c>
+      <c r="B23" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A23)</f>
+        <v>47.2518802762855</v>
+      </c>
+      <c r="C23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-19713.9784497314</v>
+      </c>
+      <c r="D23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-16639.0392632387</v>
+      </c>
+      <c r="E23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-13564.100076746</v>
+      </c>
+      <c r="F23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-10489.1608902533</v>
+      </c>
+      <c r="G23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-7414.22170376056</v>
+      </c>
+      <c r="H23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-4339.28251726785</v>
+      </c>
+      <c r="I23" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <v>-1264.34333077514</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="46" t="n">
+        <f aca="false">A23+Assumptions!$C$60</f>
+        <v>0.2</v>
+      </c>
+      <c r="B24" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A24)</f>
+        <v>51.5475057559478</v>
+      </c>
+      <c r="C24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-24834.3640214889</v>
+      </c>
+      <c r="D24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-21759.4248349962</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-18684.4856485034</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-15609.5464620107</v>
+      </c>
+      <c r="G24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-12534.607275518</v>
+      </c>
+      <c r="H24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-9459.66808902533</v>
+      </c>
+      <c r="I24" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <v>-6384.72890253262</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="46" t="n">
+        <f aca="false">A24+Assumptions!$C$60</f>
+        <v>0.3</v>
+      </c>
+      <c r="B25" s="48" t="n">
+        <f aca="false">Assumptions!$C$41*(1+A25)</f>
+        <v>55.8431312356101</v>
+      </c>
+      <c r="C25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-29954.7495932463</v>
+      </c>
+      <c r="D25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-26879.8104067536</v>
+      </c>
+      <c r="E25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-23804.8712202609</v>
+      </c>
+      <c r="F25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-20729.9320337682</v>
+      </c>
+      <c r="G25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-17654.9928472755</v>
+      </c>
+      <c r="H25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-14580.0536607828</v>
+      </c>
+      <c r="I25" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <v>-11505.1144742901</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C7:I13">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:I25">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" s="50" t="n">
+        <f aca="false">Assumptions!$C$61</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="51" t="n">
+        <f aca="false">Assumptions!$C$68</f>
+        <v>-8443.71450498848</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" s="52" t="n">
+        <f aca="false">B$4</f>
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*Assumptions!$C$9*(1+B8)+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-2293.83613200307</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <f aca="false">C8-$B$5</f>
+        <v>6149.87837298541</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <f aca="false">IF($B$5&gt;=0,"n/a",D8/-$B$5)</f>
+        <v>0.728338028169014</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <f aca="false">C8/Assumptions!$C$10</f>
+        <v>-1.92435917114351</v>
+      </c>
+      <c r="G8" s="53" t="n">
+        <f aca="false">RANK(D8,$D$8:$D$11)+COUNTIF($D$7:D7,D8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="52" t="n">
+        <f aca="false">B$4</f>
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+B9)*(Assumptions!$C$63*Assumptions!$C$9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-6087.8449731389</v>
+      </c>
+      <c r="D9" s="38" t="n">
+        <f aca="false">C9-$B$5</f>
+        <v>2355.86953184958</v>
+      </c>
+      <c r="E9" s="45" t="n">
+        <f aca="false">IF($B$5&gt;=0,"n/a",D9/-$B$5)</f>
+        <v>0.27900866738895</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <f aca="false">C9/(Assumptions!$C$10*(1+B9))</f>
+        <v>-4.64295681294913</v>
+      </c>
+      <c r="G9" s="53" t="n">
+        <f aca="false">RANK(D9,$D$8:$D$11)+COUNTIF($D$7:D8,D9)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="52" t="n">
+        <f aca="false">-B$4</f>
+        <v>-0.1</v>
+      </c>
+      <c r="C10" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*Assumptions!$C$9+Assumptions!$C$64-Assumptions!$C$41*(1+B10))-Assumptions!$C$44</f>
+        <v>-3323.32893323101</v>
+      </c>
+      <c r="D10" s="38" t="n">
+        <f aca="false">C10-$B$5</f>
+        <v>5120.38557175748</v>
+      </c>
+      <c r="E10" s="45" t="n">
+        <f aca="false">IF($B$5&gt;=0,"n/a",D10/-$B$5)</f>
+        <v>0.606413867822318</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <f aca="false">C10/Assumptions!$C$10</f>
+        <v>-2.7880276285495</v>
+      </c>
+      <c r="G10" s="53" t="n">
+        <f aca="false">RANK(D10,$D$8:$D$11)+COUNTIF($D$7:D9,D10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="52" t="n">
+        <f aca="false">B$4</f>
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*Assumptions!$C$9+Assumptions!$C$64+Assumptions!$C$38*B11-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <v>-6052.39600920951</v>
+      </c>
+      <c r="D11" s="38" t="n">
+        <f aca="false">C11-$B$5</f>
+        <v>2391.31849577897</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <f aca="false">IF($B$5&gt;=0,"n/a",D11/-$B$5)</f>
+        <v>0.28320693391116</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <f aca="false">C11/Assumptions!$C$10</f>
+        <v>-5.07751343054489</v>
+      </c>
+      <c r="G11" s="53" t="n">
+        <f aca="false">RANK(D11,$D$8:$D$11)+COUNTIF($D$7:D10,D11)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="54" t="n">
+        <f aca="false">ROWS($A$15:A15)</f>
+        <v>1</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f aca="false">INDEX($A$8:$A$11,MATCH(A15,$G$8:$G$11,0))</f>
+        <v>Order value up</v>
+      </c>
+      <c r="C15" s="38" t="n">
+        <f aca="false">INDEX($D$8:$D$11,MATCH(A15,$G$8:$G$11,0))</f>
+        <v>6149.87837298541</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <f aca="false">INDEX($E$8:$E$11,MATCH(A15,$G$8:$G$11,0))</f>
+        <v>0.728338028169014</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="n">
+        <f aca="false">ROWS($A$15:A16)</f>
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f aca="false">INDEX($A$8:$A$11,MATCH(A16,$G$8:$G$11,0))</f>
+        <v>Delivery cost per order down</v>
+      </c>
+      <c r="C16" s="38" t="n">
+        <f aca="false">INDEX($D$8:$D$11,MATCH(A16,$G$8:$G$11,0))</f>
+        <v>5120.38557175748</v>
+      </c>
+      <c r="D16" s="45" t="n">
+        <f aca="false">INDEX($E$8:$E$11,MATCH(A16,$G$8:$G$11,0))</f>
+        <v>0.606413867822318</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="54" t="n">
+        <f aca="false">ROWS($A$15:A17)</f>
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f aca="false">INDEX($A$8:$A$11,MATCH(A17,$G$8:$G$11,0))</f>
+        <v>Ad income per order up</v>
+      </c>
+      <c r="C17" s="38" t="n">
+        <f aca="false">INDEX($D$8:$D$11,MATCH(A17,$G$8:$G$11,0))</f>
+        <v>2391.31849577897</v>
+      </c>
+      <c r="D17" s="45" t="n">
+        <f aca="false">INDEX($E$8:$E$11,MATCH(A17,$G$8:$G$11,0))</f>
+        <v>0.28320693391116</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="n">
+        <f aca="false">ROWS($A$15:A18)</f>
+        <v>4</v>
+      </c>
+      <c r="B18" s="5" t="str">
+        <f aca="false">INDEX($A$8:$A$11,MATCH(A18,$G$8:$G$11,0))</f>
+        <v>Orders per day up</v>
+      </c>
+      <c r="C18" s="38" t="n">
+        <f aca="false">INDEX($D$8:$D$11,MATCH(A18,$G$8:$G$11,0))</f>
+        <v>2355.86953184958</v>
+      </c>
+      <c r="D18" s="45" t="n">
+        <f aca="false">INDEX($E$8:$E$11,MATCH(A18,$G$8:$G$11,0))</f>
+        <v>0.27900866738895</v>
       </c>
     </row>
   </sheetData>

--- a/excel/quick_commerce_model.xlsx
+++ b/excel/quick_commerce_model.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Break-even" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Lever ranking" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Scenarios" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="364">
   <si>
     <t xml:space="preserve">Assumptions: synthetic quick-commerce dark store, calibrated to Swiggy Instamart Q2 FY27 (quarter ended 30-Sep-2026)</t>
   </si>
@@ -159,6 +160,36 @@
     <t xml:space="preserve">13</t>
   </si>
   <si>
+    <t xml:space="preserve">I05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active dark stores at end of quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net order value per order, growth year on year (506 from 485)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% YoY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per dark store per day, growth quarter on quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% QoQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported (mgmt)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Derived from the anchors (formulas)</t>
   </si>
   <si>
@@ -474,7 +505,121 @@
     <t xml:space="preserve">Store contribution per day at base</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Model checks</t>
+    <t xml:space="preserve">10. Day 4 scenario settings (change vs base case; low / central / high)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 1, bundling: order value up, low case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 1, bundling: order value up, central case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equals the reported year-on-year growth in net order value (I18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 1, bundling: order value up, high case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement, about twice the central case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 2, more orders per store: low case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 2, more orders per store: central case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equals the reported quarter-on-quarter gain in orders per store per day (I19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 2, more orders per store: high case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement. Blinkit's derived figure is about 44% above Instamart's, so this stays below it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 3, lower delivery cost per order: low case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement. Negative = cheaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 3, lower delivery cost per order: central case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 3, lower delivery cost per order: high case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of Instamart's stores where the fixes are rolled out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of stores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set below 100% to model a partial rollout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stores in the rollout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported store count x share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convention for annual figures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupees per crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 crore = 10,000,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Model checks</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue split residual is not negative</t>
@@ -501,6 +646,12 @@
     <t xml:space="preserve">Lever ranking base equals Store daily P&amp;L (only when all levers are 0)</t>
   </si>
   <si>
+    <t xml:space="preserve">Scenarios base row equals the Day 3 base contribution per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low &lt;= Central &lt;= High for every scenario</t>
+  </si>
+  <si>
     <t xml:space="preserve">Per-order P&amp;L (INR per order)</t>
   </si>
   <si>
@@ -817,6 +968,156 @@
   </si>
   <si>
     <t xml:space="preserve">Ranked, largest profit impact first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenarios: base case plus three fixes (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeled scenarios for a synthetic store calibrated to Swiggy Instamart Q2 FY27. Not company measurements. Each fix has a low, central and high case; results are ranges, not single numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Fix settings (change vs base case; edit them on the Assumptions sheet, section 10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis of the central case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 1: bundling raises order value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equals Instamart's reported year-on-year gain in net order value (4.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 2: more orders per store per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equals the reported quarter-on-quarter gain in orders per store per day (9.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 3: lower delivery cost per order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement (negative = cheaper); no company figure to anchor it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported Instamart store count x rollout share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Summary: improvement versus the base case, shown as a range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per store per month, INR: Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Across stores per month, INR crore: Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Across stores per year, INR crore: Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store breaks even at central?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 1 alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 2 alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 3 alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All three fixes together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base case: store contribution per store per month (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base case: contribution across the stores per month (INR crore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Detail (every row is a formula from the Assumptions sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order value change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per day change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per store per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOV per order, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost per order, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM2 per order, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store contribution per order, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per store per day, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per store per month, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improvement vs base per store per month, INR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improvement across stores per month, INR crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improvement across stores per year, INR crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break even?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix 1 and Fix 2 central cases equal movements Instamart actually reported; Fix 3 and all low and high cases are judgement ranges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improvements are treated as steady state and applied to every store in the rollout at once. Real rollouts are gradual, so near-term results would be smaller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark store fixed cost per day stays unchanged when orders per day rise. Central costs, one-time costs of bundling or automation, and any cannibalisation are excluded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The fixes combine multiplicatively in the detail rows, so the combined result is not simply the sum of the three single-fix results.</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1228,6 +1529,34 @@
     </xf>
     <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1512,7 +1841,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1784,177 +2113,190 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
+      <c r="A17" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="B17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="18" t="n">
+        <v>48</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5"/>
+      <c r="B20" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="18" t="n">
         <f aca="false">$C$12*10000000/($C$11*1000000)</f>
         <v>708.365310821182</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
-      <c r="B18" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="18" t="n">
+      <c r="E20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5"/>
+      <c r="B21" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <f aca="false">$C$13*10000000/($C$11*1000000)</f>
         <v>100.306983883346</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <f aca="false">$C$14*$C$17</f>
+      <c r="E21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5"/>
+      <c r="B22" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <f aca="false">$C$14*$C$20</f>
         <v>-7.08365310821182</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="18" t="n">
-        <f aca="false">$C$18-$C$19</f>
-        <v>107.390636991558</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="12" t="s">
+      <c r="E22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="F22" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="14"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>60</v>
-      </c>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
       <c r="B23" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0.2</v>
+        <v>62</v>
+      </c>
+      <c r="C23" s="18" t="n">
+        <f aca="false">$C$21-$C$22</f>
+        <v>107.390636991558</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="19" t="n">
-        <f aca="false">1-$C$22-$C$23</f>
-        <v>0.2</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="12" t="s">
+      <c r="A24" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="14"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
@@ -1964,156 +2306,165 @@
         <v>66</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="A27" s="5"/>
       <c r="B27" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="17" t="n">
-        <v>0.15</v>
+        <v>73</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <f aca="false">1-$C$25-$C$26</f>
+        <v>0.2</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C28" s="17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
+      <c r="A29" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="B29" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="19" t="n">
-        <f aca="false">1-$C$25-$C$26-$C$27-$C$28</f>
-        <v>0.25</v>
+        <v>80</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>0.4</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
+      <c r="A31" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="A32" s="5"/>
       <c r="B32" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <f aca="false">1-$C$28-$C$29-$C$30-$C$31</f>
+        <v>0.25</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>86</v>
@@ -2128,91 +2479,92 @@
       <c r="B33" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="20" t="n">
-        <v>0</v>
+      <c r="C33" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="14"/>
+      <c r="A34" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+      <c r="A36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
+      <c r="A37" s="5" t="s">
+        <v>99</v>
+      </c>
       <c r="B37" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="19" t="n">
-        <f aca="false">$C$22*$C$18/$C$9</f>
-        <v>0.118941087608711</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>96</v>
@@ -2221,76 +2573,74 @@
       <c r="H37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
+      <c r="A38" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="B38" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="18" t="n">
-        <f aca="false">$C$23*$C$18</f>
-        <v>20.0613967766692</v>
+        <v>102</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="12"/>
+        <v>95</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="14"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="18" t="n">
-        <f aca="false">$C$24*$C$18</f>
-        <v>20.0613967766692</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="14"/>
+      <c r="A39" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
       <c r="B40" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" s="18" t="n">
-        <f aca="false">$C$25*$C$20</f>
-        <v>12.886876438987</v>
+        <v>104</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <f aca="false">$C$25*$C$21/$C$9</f>
+        <v>0.118941087608711</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="14"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="12" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C41" s="18" t="n">
-        <f aca="false">$C$26*$C$20</f>
-        <v>42.9562547966232</v>
+        <f aca="false">$C$26*$C$21</f>
+        <v>20.0613967766692</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="5"/>
@@ -2299,17 +2649,17 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="12" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C42" s="18" t="n">
-        <f aca="false">$C$27*$C$20</f>
-        <v>16.1085955487337</v>
+        <f aca="false">$C$27*$C$21</f>
+        <v>20.0613967766692</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="5"/>
@@ -2318,491 +2668,491 @@
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
       <c r="B43" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="19" t="n">
-        <f aca="false">$C$28*$C$20/$C$9</f>
-        <v>0.01697875683661</v>
+        <v>109</v>
+      </c>
+      <c r="C43" s="18" t="n">
+        <f aca="false">$C$28*$C$23</f>
+        <v>12.886876438987</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>103</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F43" s="12"/>
       <c r="G43" s="5"/>
       <c r="H43" s="14"/>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
       <c r="B44" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C44" s="21" t="n">
-        <f aca="false">$C$29*$C$20*$C$10</f>
-        <v>32002.4098234843</v>
+        <v>110</v>
+      </c>
+      <c r="C44" s="18" t="n">
+        <f aca="false">$C$29*$C$23</f>
+        <v>42.9562547966232</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>106</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F44" s="12"/>
       <c r="G44" s="5"/>
       <c r="H44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="18" t="n">
+        <f aca="false">$C$30*$C$23</f>
+        <v>16.1085955487337</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="14"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
       <c r="B46" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="18" t="n">
-        <f aca="false">$C$9*(1+$C$32)</f>
-        <v>506</v>
+        <v>112</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <f aca="false">$C$31*$C$23/$C$9</f>
+        <v>0.01697875683661</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>113</v>
+      </c>
       <c r="G46" s="5"/>
       <c r="H46" s="14"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
       <c r="B47" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C47" s="21" t="n">
-        <f aca="false">$C$10*(1+$C$33)</f>
-        <v>1192</v>
+        <f aca="false">$C$32*$C$23*$C$10</f>
+        <v>32002.4098234843</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F47" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="G47" s="5"/>
       <c r="H47" s="14"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="B48" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="18" t="n">
-        <f aca="false">$C$41*(1+$C$34)</f>
-        <v>42.9562547966232</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="14"/>
+      <c r="A48" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
       <c r="B49" s="12" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C49" s="18" t="n">
-        <f aca="false">$C$38*(1+$C$35)</f>
-        <v>20.0613967766692</v>
+        <f aca="false">$C$9*(1+$C$35)</f>
+        <v>506</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="5"/>
       <c r="H49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="A50" s="5"/>
+      <c r="B50" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <f aca="false">$C$10*(1+$C$36)</f>
+        <v>1192</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="14"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5"/>
       <c r="B51" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>28</v>
+        <v>121</v>
+      </c>
+      <c r="C51" s="18" t="n">
+        <f aca="false">$C$44*(1+$C$37)</f>
+        <v>42.9562547966232</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>118</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F51" s="12"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="14"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="A52" s="5"/>
       <c r="B52" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C52" s="15" t="n">
-        <v>525</v>
+        <v>122</v>
+      </c>
+      <c r="C52" s="18" t="n">
+        <f aca="false">$C$41*(1+$C$38)</f>
+        <v>20.0613967766692</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="G52" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C53" s="15" t="n">
-        <v>1718</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
+      <c r="H54" s="14" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B55" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>525</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="17" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="F55" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H55" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="C56" s="17" t="n">
-        <v>0.05</v>
+        <v>133</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>1718</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F56" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="14"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="17" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="14"/>
+      <c r="A57" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="14"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>-0.3</v>
+        <v>0.05</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="14"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="F60" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="C60" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>128</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="14"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C61" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="14"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-    </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5"/>
+      <c r="A62" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="14"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>147</v>
+      </c>
       <c r="B63" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" s="22" t="n">
-        <f aca="false">$C$37-$C$43</f>
-        <v>0.101962330772101</v>
+        <v>148</v>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F63" s="12"/>
+        <v>137</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5"/>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="B64" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C64" s="18" t="n">
-        <f aca="false">$C$38+$C$39-$C$40-$C$42</f>
-        <v>11.1273215656178</v>
+        <v>150</v>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F64" s="12"/>
+        <v>137</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>151</v>
+      </c>
       <c r="G64" s="5"/>
       <c r="H64" s="14"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5"/>
-      <c r="B65" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="18" t="n">
-        <f aca="false">$C$44/$C$10</f>
-        <v>26.8476592478895</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F65" s="12"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="14"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
       <c r="B66" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="C66" s="18" t="n">
-        <f aca="false">$C$63*$C$9+$C$64-$C$41</f>
-        <v>19.7640061396777</v>
+        <v>153</v>
+      </c>
+      <c r="C66" s="22" t="n">
+        <f aca="false">$C$40-$C$46</f>
+        <v>0.101962330772101</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="5"/>
       <c r="H66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
       <c r="B67" s="12" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C67" s="18" t="n">
-        <f aca="false">$C$66-$C$65</f>
-        <v>-7.08365310821181</v>
+        <f aca="false">$C$41+$C$42-$C$43-$C$45</f>
+        <v>11.1273215656178</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="5"/>
@@ -2811,46 +3161,55 @@
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
       <c r="B68" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" s="21" t="n">
-        <f aca="false">$C$67*$C$10</f>
-        <v>-8443.71450498848</v>
+        <v>155</v>
+      </c>
+      <c r="C68" s="18" t="n">
+        <f aca="false">$C$47/$C$10</f>
+        <v>26.8476592478895</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="5"/>
       <c r="H68" s="14"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
+      <c r="A69" s="5"/>
+      <c r="B69" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C69" s="18" t="n">
+        <f aca="false">$C$66*$C$9+$C$67-$C$44</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="14"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
       <c r="B70" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70" s="23" t="str">
-        <f aca="false">IF($C$24&gt;=0,"OK","CHECK")</f>
-        <v>OK</v>
-      </c>
-      <c r="D70" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="C70" s="18" t="n">
+        <f aca="false">$C$69-$C$68</f>
+        <v>-7.08365310821181</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E70" s="5" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="F70" s="12"/>
       <c r="G70" s="5"/>
@@ -2859,104 +3218,481 @@
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
       <c r="B71" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C71" s="23" t="str">
-        <f aca="false">IF($C$29&gt;=0,"OK","CHECK")</f>
-        <v>OK</v>
-      </c>
-      <c r="D71" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="C71" s="21" t="n">
+        <f aca="false">$C$70*$C$10</f>
+        <v>-8443.71450498848</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="E71" s="5" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="F71" s="12"/>
       <c r="G71" s="5"/>
       <c r="H71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="B72" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C72" s="23" t="str">
-        <f aca="false">IF(ABS($C$32)+ABS($C$33)+ABS($C$34)+ABS($C$35)&gt;0,"Levers on: n/a",IF(ABS('Per-order P&amp;L'!$B$19-$C$19)&lt;0.000001,"OK","CHECK"))</f>
-        <v>OK</v>
-      </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="14"/>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5"/>
+      <c r="A73" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="B73" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C73" s="23" t="str">
-        <f aca="false">IF(ABS('Store daily P&amp;L'!$B$19/'Store daily P&amp;L'!$B$4-'Per-order P&amp;L'!$B$19)&lt;0.000001,"OK","CHECK")</f>
-        <v>OK</v>
-      </c>
-      <c r="D73" s="5"/>
+        <v>161</v>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="E73" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F73" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="G73" s="5"/>
       <c r="H73" s="14"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
       <c r="B74" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C74" s="23" t="str">
-        <f aca="false">IF(ABS($C$67-$C$19)&lt;0.000001,"OK","CHECK")</f>
-        <v>OK</v>
-      </c>
-      <c r="D74" s="5"/>
+        <v>163</v>
+      </c>
+      <c r="C74" s="19" t="n">
+        <f aca="false">$C$17</f>
+        <v>0.043</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="E74" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F74" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>164</v>
+      </c>
       <c r="G74" s="5"/>
       <c r="H74" s="14"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5"/>
+      <c r="A75" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="B75" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" s="23" t="str">
+        <v>166</v>
+      </c>
+      <c r="C75" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="14"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G76" s="5"/>
+      <c r="H76" s="14"/>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5"/>
+      <c r="B77" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" s="19" t="n">
+        <f aca="false">$C$18</f>
+        <v>0.095</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="14"/>
+    </row>
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" s="5"/>
+      <c r="H78" s="14"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="17" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G79" s="5"/>
+      <c r="H79" s="14"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="17" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G80" s="5"/>
+      <c r="H80" s="14"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="17" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G81" s="5"/>
+      <c r="H81" s="14"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G82" s="5"/>
+      <c r="H82" s="14"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5"/>
+      <c r="B83" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" s="21" t="n">
+        <f aca="false">$C$16*$C$82</f>
+        <v>1240</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G83" s="5"/>
+      <c r="H83" s="14"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C84" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G84" s="5"/>
+      <c r="H84" s="14"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C85" s="15" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G85" s="5"/>
+      <c r="H85" s="14"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5"/>
+      <c r="B87" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C87" s="23" t="str">
+        <f aca="false">IF($C$27&gt;=0,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" s="12"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="14"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5"/>
+      <c r="B88" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C88" s="23" t="str">
+        <f aca="false">IF($C$32&gt;=0,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F88" s="12"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="14"/>
+    </row>
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5"/>
+      <c r="B89" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="23" t="str">
+        <f aca="false">IF(ABS($C$35)+ABS($C$36)+ABS($C$37)+ABS($C$38)&gt;0,"Levers on: n/a",IF(ABS('Per-order P&amp;L'!$B$19-$C$22)&lt;0.000001,"OK","CHECK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F89" s="12"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="14"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5"/>
+      <c r="B90" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C90" s="23" t="str">
+        <f aca="false">IF(ABS('Store daily P&amp;L'!$B$19/'Store daily P&amp;L'!$B$4-'Per-order P&amp;L'!$B$19)&lt;0.000001,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="14"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5"/>
+      <c r="B91" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C91" s="23" t="str">
+        <f aca="false">IF(ABS($C$70-$C$22)&lt;0.000001,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F91" s="12"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="14"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5"/>
+      <c r="B92" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C92" s="23" t="str">
         <f aca="false">IF(ISNUMBER('Break-even'!$B$8),IF(ABS('Break-even'!$B$8*'Break-even'!$B$7-'Break-even'!$B$6)&lt;0.001,"OK","CHECK"),"n/a")</f>
         <v>OK</v>
       </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="14"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5"/>
-      <c r="B76" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C76" s="23" t="str">
-        <f aca="false">IF(ABS($C$32)+ABS($C$33)+ABS($C$34)+ABS($C$35)&gt;0,"Levers on: n/a",IF(ABS('Lever ranking'!$B$5-'Store daily P&amp;L'!$B$19)&lt;0.001,"OK","CHECK"))</f>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F92" s="12"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="14"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5"/>
+      <c r="B93" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C93" s="23" t="str">
+        <f aca="false">IF(ABS($C$35)+ABS($C$36)+ABS($C$37)+ABS($C$38)&gt;0,"Levers on: n/a",IF(ABS('Lever ranking'!$B$5-'Store daily P&amp;L'!$B$19)&lt;0.001,"OK","CHECK"))</f>
         <v>OK</v>
       </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="14"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F93" s="12"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="14"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5"/>
+      <c r="B94" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C94" s="23" t="str">
+        <f aca="false">IF(ABS(Scenarios!$K$27-$C$71)&lt;0.001,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="14"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="5"/>
+      <c r="B95" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C95" s="23" t="str">
+        <f aca="false">IF(AND(Scenarios!$B$18&lt;=Scenarios!$C$18,Scenarios!$C$18&lt;=Scenarios!$D$18,Scenarios!$B$19&lt;=Scenarios!$C$19,Scenarios!$C$19&lt;=Scenarios!$D$19,Scenarios!$B$20&lt;=Scenarios!$C$20,Scenarios!$C$20&lt;=Scenarios!$D$20,Scenarios!$B$21&lt;=Scenarios!$C$21,Scenarios!$C$21&lt;=Scenarios!$D$21),"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" s="12"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2988,17 +3724,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -3006,24 +3742,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">Assumptions!$C$46</f>
+        <f aca="false">Assumptions!$C$49</f>
         <v>506</v>
       </c>
       <c r="C6" s="28" t="n">
@@ -3031,15 +3767,15 @@
         <v>1</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="B7" s="30" t="n">
-        <f aca="false">-B6*(1-Assumptions!$C$37)</f>
+        <f aca="false">-B6*(1-Assumptions!$C$40)</f>
         <v>-445.815809669992</v>
       </c>
       <c r="C7" s="31" t="n">
@@ -3047,12 +3783,12 @@
         <v>-0.881058912391289</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="B8" s="30" t="n">
         <f aca="false">B6+B7</f>
@@ -3063,15 +3799,15 @@
         <v>0.118941087608711</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="B9" s="33" t="n">
-        <f aca="false">Assumptions!$C$49</f>
+        <f aca="false">Assumptions!$C$52</f>
         <v>20.0613967766692</v>
       </c>
       <c r="C9" s="31" t="n">
@@ -3079,15 +3815,15 @@
         <v>0.0396470292029036</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="B10" s="33" t="n">
-        <f aca="false">Assumptions!$C$39</f>
+        <f aca="false">Assumptions!$C$42</f>
         <v>20.0613967766692</v>
       </c>
       <c r="C10" s="31" t="n">
@@ -3095,12 +3831,12 @@
         <v>0.0396470292029036</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">B8+B9+B10</f>
@@ -3111,15 +3847,15 @@
         <v>0.198235146014518</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="B12" s="30" t="n">
-        <f aca="false">-Assumptions!$C$40</f>
+        <f aca="false">-Assumptions!$C$43</f>
         <v>-12.886876438987</v>
       </c>
       <c r="C12" s="31" t="n">
@@ -3130,7 +3866,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="B13" s="34" t="n">
         <f aca="false">B11+B12</f>
@@ -3141,15 +3877,15 @@
         <v>0.172767010759603</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>176</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="B14" s="30" t="n">
-        <f aca="false">-Assumptions!$C$42</f>
+        <f aca="false">-Assumptions!$C$45</f>
         <v>-16.1085955487337</v>
       </c>
       <c r="C14" s="31" t="n">
@@ -3160,10 +3896,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="B15" s="30" t="n">
-        <f aca="false">-Assumptions!$C$48</f>
+        <f aca="false">-Assumptions!$C$51</f>
         <v>-42.9562547966232</v>
       </c>
       <c r="C15" s="31" t="n">
@@ -3171,15 +3907,15 @@
         <v>-0.0848937841830497</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="B16" s="30" t="n">
-        <f aca="false">-B6*Assumptions!$C$43</f>
+        <f aca="false">-B6*Assumptions!$C$46</f>
         <v>-8.59125095932463</v>
       </c>
       <c r="C16" s="31" t="n">
@@ -3187,12 +3923,12 @@
         <v>-0.01697875683661</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="B17" s="34" t="n">
         <f aca="false">B13+B14+B15+B16</f>
@@ -3203,15 +3939,15 @@
         <v>0.0390593006712997</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="B18" s="30" t="n">
-        <f aca="false">IF(Assumptions!$C$47=0,0,-Assumptions!$C$44/Assumptions!$C$47)</f>
+        <f aca="false">IF(Assumptions!$C$50=0,0,-Assumptions!$C$47/Assumptions!$C$50)</f>
         <v>-26.8476592478895</v>
       </c>
       <c r="C18" s="31" t="n">
@@ -3219,12 +3955,12 @@
         <v>-0.0530586151144061</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">B17+B18</f>
@@ -3235,38 +3971,38 @@
         <v>-0.0139993144431063</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>188</v>
+        <v>238</v>
       </c>
       <c r="B22" s="33" t="n">
-        <f aca="false">Assumptions!$C$19</f>
+        <f aca="false">Assumptions!$C$22</f>
         <v>-7.08365310821182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">B19-B22</f>
         <v>0</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="B24" s="33" t="n">
         <f aca="false">Assumptions!$C$15</f>
@@ -3275,22 +4011,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="B25" s="30" t="n">
         <f aca="false">B19-B24</f>
         <v>-37.0836531082118</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="B26" s="33" t="n">
-        <f aca="false">Assumptions!$C$51</f>
+        <f aca="false">Assumptions!$C$54</f>
         <v>28</v>
       </c>
     </row>
@@ -3323,273 +4059,273 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="B4" s="35" t="n">
-        <f aca="false">Assumptions!$C$47</f>
+        <f aca="false">Assumptions!$C$50</f>
         <v>1192</v>
       </c>
       <c r="C4" s="36" t="n">
-        <f aca="false">B4*Assumptions!$C$30</f>
+        <f aca="false">B4*Assumptions!$C$33</f>
         <v>35760</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B6" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B6</f>
         <v>603152</v>
       </c>
       <c r="C6" s="37" t="n">
-        <f aca="false">B6*Assumptions!$C$30</f>
+        <f aca="false">B6*Assumptions!$C$33</f>
         <v>18094560</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="B7" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B7</f>
         <v>-531412.445126631</v>
       </c>
       <c r="C7" s="38" t="n">
-        <f aca="false">B7*Assumptions!$C$30</f>
+        <f aca="false">B7*Assumptions!$C$33</f>
         <v>-15942373.3537989</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="B8" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B8</f>
         <v>71739.5548733691</v>
       </c>
       <c r="C8" s="38" t="n">
-        <f aca="false">B8*Assumptions!$C$30</f>
+        <f aca="false">B8*Assumptions!$C$33</f>
         <v>2152186.64620107</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="B9" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B9</f>
         <v>23913.1849577897</v>
       </c>
       <c r="C9" s="38" t="n">
-        <f aca="false">B9*Assumptions!$C$30</f>
+        <f aca="false">B9*Assumptions!$C$33</f>
         <v>717395.548733692</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>203</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="B10" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B10</f>
         <v>23913.1849577897</v>
       </c>
       <c r="C10" s="38" t="n">
-        <f aca="false">B10*Assumptions!$C$30</f>
+        <f aca="false">B10*Assumptions!$C$33</f>
         <v>717395.548733692</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="B11" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B11</f>
         <v>119565.924788949</v>
       </c>
       <c r="C11" s="37" t="n">
-        <f aca="false">B11*Assumptions!$C$30</f>
+        <f aca="false">B11*Assumptions!$C$33</f>
         <v>3586977.74366846</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>205</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="B12" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B12</f>
         <v>-15361.1567152724</v>
       </c>
       <c r="C12" s="38" t="n">
-        <f aca="false">B12*Assumptions!$C$30</f>
+        <f aca="false">B12*Assumptions!$C$33</f>
         <v>-460834.701458173</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="B13" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B13</f>
         <v>104204.768073676</v>
       </c>
       <c r="C13" s="37" t="n">
-        <f aca="false">B13*Assumptions!$C$30</f>
+        <f aca="false">B13*Assumptions!$C$33</f>
         <v>3126143.04221028</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>207</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="B14" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B14</f>
         <v>-19201.4458940906</v>
       </c>
       <c r="C14" s="38" t="n">
-        <f aca="false">B14*Assumptions!$C$30</f>
+        <f aca="false">B14*Assumptions!$C$33</f>
         <v>-576043.376822717</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="B15" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B15</f>
         <v>-51203.8557175748</v>
       </c>
       <c r="C15" s="38" t="n">
-        <f aca="false">B15*Assumptions!$C$30</f>
+        <f aca="false">B15*Assumptions!$C$33</f>
         <v>-1536115.67152724</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="B16" s="38" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B16</f>
         <v>-10240.771143515</v>
       </c>
       <c r="C16" s="38" t="n">
-        <f aca="false">B16*Assumptions!$C$30</f>
+        <f aca="false">B16*Assumptions!$C$33</f>
         <v>-307223.134305449</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="B17" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B17</f>
         <v>23558.6953184958</v>
       </c>
       <c r="C17" s="37" t="n">
-        <f aca="false">B17*Assumptions!$C$30</f>
+        <f aca="false">B17*Assumptions!$C$33</f>
         <v>706760.859554873</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="B18" s="38" t="n">
-        <f aca="false">-Assumptions!$C$44</f>
+        <f aca="false">-Assumptions!$C$47</f>
         <v>-32002.4098234843</v>
       </c>
       <c r="C18" s="38" t="n">
-        <f aca="false">B18*Assumptions!$C$30</f>
+        <f aca="false">B18*Assumptions!$C$33</f>
         <v>-960072.294704528</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="B19" s="37" t="n">
         <f aca="false">$B$4*'Per-order P&amp;L'!B19</f>
         <v>-8443.71450498847</v>
       </c>
       <c r="C19" s="37" t="n">
-        <f aca="false">B19*Assumptions!$C$30</f>
+        <f aca="false">B19*Assumptions!$C$33</f>
         <v>-253311.435149654</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="B22" s="30" t="n">
         <f aca="false">IF(B4=0,0,B19/B4)</f>
@@ -3598,7 +4334,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">B22-'Per-order P&amp;L'!B19</f>
@@ -3634,17 +4370,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>218</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3655,60 +4391,60 @@
         <v>10</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>220</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B6" s="41" t="n">
-        <f aca="false">Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$47</f>
         <v>32002.4098234843</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B7" s="42" t="n">
-        <f aca="false">Assumptions!$C$66</f>
+        <f aca="false">Assumptions!$C$69</f>
         <v>19.7640061396777</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>221</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="43" t="s">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="B8" s="44" t="n">
         <f aca="false">IF(B7&lt;=0,"No break-even: CM2 is not positive",B6/B7)</f>
         <v>1619.22687117756</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="B9" s="41" t="n">
         <f aca="false">Assumptions!$C$10</f>
         <v>1192</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">IF(ISNUMBER(B8),B8-B9,"n/a")</f>
@@ -3718,7 +4454,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="B11" s="45" t="n">
         <f aca="false">IF(ISNUMBER(B8),IF(B9=0,0,B8/B9-1),"n/a")</f>
@@ -3728,48 +4464,48 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="B12" s="41" t="n">
-        <f aca="false">Assumptions!$C$53</f>
+        <f aca="false">Assumptions!$C$56</f>
         <v>1718</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>229</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">IF(ISNUMBER(B8),B8-B12,"n/a")</f>
         <v>-98.7731288224447</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>232</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F16" s="40" t="s">
         <v>11</v>
@@ -3777,14 +4513,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="B17" s="42" t="n">
         <f aca="false">Assumptions!$C$9</f>
         <v>506</v>
       </c>
       <c r="C17" s="18" t="n">
-        <f aca="false">IF(Assumptions!$C$63&lt;=0,"n/a",B17-Assumptions!$C$67/Assumptions!$C$63)</f>
+        <f aca="false">IF(Assumptions!$C$66&lt;=0,"n/a",B17-Assumptions!$C$70/Assumptions!$C$66)</f>
         <v>575.473236386139</v>
       </c>
       <c r="D17" s="18" t="n">
@@ -3801,7 +4537,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="B18" s="41" t="n">
         <f aca="false">Assumptions!$C$10</f>
@@ -3820,19 +4556,19 @@
         <v>0.358411804679157</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>238</v>
+        <v>288</v>
       </c>
       <c r="B19" s="42" t="n">
-        <f aca="false">Assumptions!$C$41</f>
+        <f aca="false">Assumptions!$C$44</f>
         <v>42.9562547966232</v>
       </c>
       <c r="C19" s="18" t="n">
-        <f aca="false">B19+Assumptions!$C$67</f>
+        <f aca="false">B19+Assumptions!$C$70</f>
         <v>35.8726016884114</v>
       </c>
       <c r="D19" s="18" t="n">
@@ -3849,14 +4585,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="B20" s="42" t="n">
-        <f aca="false">Assumptions!$C$38</f>
+        <f aca="false">Assumptions!$C$41</f>
         <v>20.0613967766692</v>
       </c>
       <c r="C20" s="18" t="n">
-        <f aca="false">B20-Assumptions!$C$67</f>
+        <f aca="false">B20-Assumptions!$C$70</f>
         <v>27.145049884881</v>
       </c>
       <c r="D20" s="18" t="n">
@@ -3873,7 +4609,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -3902,58 +4638,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>242</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>243</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="C5" s="46" t="n">
-        <f aca="false">Assumptions!$C$57</f>
+        <f aca="false">Assumptions!$C$60</f>
         <v>-0.2</v>
       </c>
       <c r="D5" s="46" t="n">
-        <f aca="false">C5+Assumptions!$C$58</f>
+        <f aca="false">C5+Assumptions!$C$61</f>
         <v>-0.1</v>
       </c>
       <c r="E5" s="46" t="n">
-        <f aca="false">D5+Assumptions!$C$58</f>
+        <f aca="false">D5+Assumptions!$C$61</f>
         <v>0</v>
       </c>
       <c r="F5" s="46" t="n">
-        <f aca="false">E5+Assumptions!$C$58</f>
+        <f aca="false">E5+Assumptions!$C$61</f>
         <v>0.1</v>
       </c>
       <c r="G5" s="46" t="n">
-        <f aca="false">F5+Assumptions!$C$58</f>
+        <f aca="false">F5+Assumptions!$C$61</f>
         <v>0.2</v>
       </c>
       <c r="H5" s="46" t="n">
-        <f aca="false">G5+Assumptions!$C$58</f>
+        <f aca="false">G5+Assumptions!$C$61</f>
         <v>0.3</v>
       </c>
       <c r="I5" s="46" t="n">
-        <f aca="false">H5+Assumptions!$C$58</f>
+        <f aca="false">H5+Assumptions!$C$61</f>
         <v>0.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="C6" s="47" t="n">
         <f aca="false">Assumptions!$C$10*(1+C5)</f>
@@ -3986,7 +4722,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="46" t="n">
-        <f aca="false">Assumptions!$C$55</f>
+        <f aca="false">Assumptions!$C$58</f>
         <v>-0.1</v>
       </c>
       <c r="B7" s="48" t="n">
@@ -3994,37 +4730,37 @@
         <v>455.4</v>
       </c>
       <c r="C7" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-18075.356267076</v>
       </c>
       <c r="D7" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-16334.4745725249</v>
       </c>
       <c r="E7" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-14593.5928779739</v>
       </c>
       <c r="F7" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-12852.7111834229</v>
       </c>
       <c r="G7" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-11111.8294888718</v>
       </c>
       <c r="H7" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-9370.94779432078</v>
       </c>
       <c r="I7" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B7+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B7+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-7630.06609976975</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="n">
-        <f aca="false">A7+Assumptions!$C$56</f>
+        <f aca="false">A7+Assumptions!$C$59</f>
         <v>-0.05</v>
       </c>
       <c r="B8" s="48" t="n">
@@ -4032,37 +4768,37 @@
         <v>480.7</v>
       </c>
       <c r="C8" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-15615.4049178818</v>
       </c>
       <c r="D8" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-13567.0293046815</v>
       </c>
       <c r="E8" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-11518.6536914812</v>
       </c>
       <c r="F8" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-9470.27807828088</v>
       </c>
       <c r="G8" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-7421.90246508058</v>
       </c>
       <c r="H8" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-5373.52685188026</v>
       </c>
       <c r="I8" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B8+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B8+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-3325.15123867996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="46" t="n">
-        <f aca="false">A8+Assumptions!$C$56</f>
+        <f aca="false">A8+Assumptions!$C$59</f>
         <v>0</v>
       </c>
       <c r="B9" s="48" t="n">
@@ -4070,37 +4806,37 @@
         <v>506</v>
       </c>
       <c r="C9" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-13155.4535686876</v>
       </c>
       <c r="D9" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-10799.5840368381</v>
       </c>
       <c r="E9" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-8443.71450498848</v>
       </c>
       <c r="F9" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-6087.8449731389</v>
       </c>
       <c r="G9" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-3731.97544128933</v>
       </c>
       <c r="H9" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-1376.10590943975</v>
       </c>
       <c r="I9" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>979.763622409824</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="n">
-        <f aca="false">A9+Assumptions!$C$56</f>
+        <f aca="false">A9+Assumptions!$C$59</f>
         <v>0.05</v>
       </c>
       <c r="B10" s="48" t="n">
@@ -4108,37 +4844,37 @@
         <v>531.3</v>
       </c>
       <c r="C10" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-10695.5022194935</v>
       </c>
       <c r="D10" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-8032.13876899462</v>
       </c>
       <c r="E10" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-5368.77531849578</v>
       </c>
       <c r="F10" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-2705.41186799693</v>
       </c>
       <c r="G10" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-42.0484174980811</v>
       </c>
       <c r="H10" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>2621.31503300077</v>
       </c>
       <c r="I10" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B10+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B10+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>5284.67848349961</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="n">
-        <f aca="false">A10+Assumptions!$C$56</f>
+        <f aca="false">A10+Assumptions!$C$59</f>
         <v>0.1</v>
       </c>
       <c r="B11" s="48" t="n">
@@ -4146,37 +4882,37 @@
         <v>556.6</v>
       </c>
       <c r="C11" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-8235.55087029931</v>
       </c>
       <c r="D11" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-5264.69350115119</v>
       </c>
       <c r="E11" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-2293.83613200307</v>
       </c>
       <c r="F11" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>677.021237145051</v>
       </c>
       <c r="G11" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>3647.87860629316</v>
       </c>
       <c r="H11" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>6618.73597544129</v>
       </c>
       <c r="I11" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B11+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B11+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>9589.5933445894</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="n">
-        <f aca="false">A11+Assumptions!$C$56</f>
+        <f aca="false">A11+Assumptions!$C$59</f>
         <v>0.15</v>
       </c>
       <c r="B12" s="48" t="n">
@@ -4184,37 +4920,37 @@
         <v>581.9</v>
       </c>
       <c r="C12" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-5775.59952110514</v>
       </c>
       <c r="D12" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-2497.24823330775</v>
       </c>
       <c r="E12" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>781.103054489635</v>
       </c>
       <c r="F12" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>4059.45434228703</v>
       </c>
       <c r="G12" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>7337.80563008441</v>
       </c>
       <c r="H12" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>10616.1569178818</v>
       </c>
       <c r="I12" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B12+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B12+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>13894.5082056792</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="n">
-        <f aca="false">A12+Assumptions!$C$56</f>
+        <f aca="false">A12+Assumptions!$C$59</f>
         <v>0.2</v>
       </c>
       <c r="B13" s="48" t="n">
@@ -4222,78 +4958,78 @@
         <v>607.2</v>
       </c>
       <c r="C13" s="38" t="n">
-        <f aca="false">C$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">C$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-3315.64817191098</v>
       </c>
       <c r="D13" s="38" t="n">
-        <f aca="false">D$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">D$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>270.197034535682</v>
       </c>
       <c r="E13" s="38" t="n">
-        <f aca="false">E$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">E$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>3856.04224098234</v>
       </c>
       <c r="F13" s="38" t="n">
-        <f aca="false">F$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">F$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>7441.88744742901</v>
       </c>
       <c r="G13" s="38" t="n">
-        <f aca="false">G$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">G$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>11027.7326538757</v>
       </c>
       <c r="H13" s="38" t="n">
-        <f aca="false">H$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">H$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>14613.5778603223</v>
       </c>
       <c r="I13" s="38" t="n">
-        <f aca="false">I$6*(Assumptions!$C$63*$B13+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">I$6*(Assumptions!$C$66*$B13+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>18199.423066769</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C17" s="46" t="n">
-        <f aca="false">Assumptions!$C$55</f>
+        <f aca="false">Assumptions!$C$58</f>
         <v>-0.1</v>
       </c>
       <c r="D17" s="46" t="n">
-        <f aca="false">C17+Assumptions!$C$56</f>
+        <f aca="false">C17+Assumptions!$C$59</f>
         <v>-0.05</v>
       </c>
       <c r="E17" s="46" t="n">
-        <f aca="false">D17+Assumptions!$C$56</f>
+        <f aca="false">D17+Assumptions!$C$59</f>
         <v>0</v>
       </c>
       <c r="F17" s="46" t="n">
-        <f aca="false">E17+Assumptions!$C$56</f>
+        <f aca="false">E17+Assumptions!$C$59</f>
         <v>0.05</v>
       </c>
       <c r="G17" s="46" t="n">
-        <f aca="false">F17+Assumptions!$C$56</f>
+        <f aca="false">F17+Assumptions!$C$59</f>
         <v>0.1</v>
       </c>
       <c r="H17" s="46" t="n">
-        <f aca="false">G17+Assumptions!$C$56</f>
+        <f aca="false">G17+Assumptions!$C$59</f>
         <v>0.15</v>
       </c>
       <c r="I17" s="46" t="n">
-        <f aca="false">H17+Assumptions!$C$56</f>
+        <f aca="false">H17+Assumptions!$C$59</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="C18" s="49" t="n">
         <f aca="false">Assumptions!$C$9*(1+C17)</f>
@@ -4326,267 +5062,267 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="n">
-        <f aca="false">Assumptions!$C$59</f>
+        <f aca="false">Assumptions!$C$62</f>
         <v>-0.3</v>
       </c>
       <c r="B19" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A19)</f>
+        <f aca="false">Assumptions!$C$44*(1+A19)</f>
         <v>30.0693783576362</v>
       </c>
       <c r="C19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>767.563837298556</v>
       </c>
       <c r="D19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>3842.50302379126</v>
       </c>
       <c r="E19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>6917.44221028397</v>
       </c>
       <c r="F19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>9992.38139677668</v>
       </c>
       <c r="G19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>13067.3205832694</v>
       </c>
       <c r="H19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>16142.2597697621</v>
       </c>
       <c r="I19" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B19)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B19)-Assumptions!$C$47</f>
         <v>19217.1989562548</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="46" t="n">
-        <f aca="false">A19+Assumptions!$C$60</f>
+        <f aca="false">A19+Assumptions!$C$63</f>
         <v>-0.2</v>
       </c>
       <c r="B20" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A20)</f>
+        <f aca="false">Assumptions!$C$44*(1+A20)</f>
         <v>34.3650038372985</v>
       </c>
       <c r="C20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>-4352.82173445893</v>
       </c>
       <c r="D20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>-1277.88254796622</v>
       </c>
       <c r="E20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>1797.05663852648</v>
       </c>
       <c r="F20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>4871.99582501919</v>
       </c>
       <c r="G20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>7946.93501151189</v>
       </c>
       <c r="H20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>11021.8741980046</v>
       </c>
       <c r="I20" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B20)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B20)-Assumptions!$C$47</f>
         <v>14096.8133844973</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="46" t="n">
-        <f aca="false">A20+Assumptions!$C$60</f>
+        <f aca="false">A20+Assumptions!$C$63</f>
         <v>-0.1</v>
       </c>
       <c r="B21" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A21)</f>
+        <f aca="false">Assumptions!$C$44*(1+A21)</f>
         <v>38.6606293169609</v>
       </c>
       <c r="C21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>-9473.20730621642</v>
       </c>
       <c r="D21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>-6398.26811972371</v>
       </c>
       <c r="E21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>-3323.32893323101</v>
       </c>
       <c r="F21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>-248.389746738299</v>
       </c>
       <c r="G21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>2826.54943975441</v>
       </c>
       <c r="H21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>5901.48862624711</v>
       </c>
       <c r="I21" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B21)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B21)-Assumptions!$C$47</f>
         <v>8976.42781273982</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="46" t="n">
-        <f aca="false">A21+Assumptions!$C$60</f>
+        <f aca="false">A21+Assumptions!$C$63</f>
         <v>0</v>
       </c>
       <c r="B22" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A22)</f>
+        <f aca="false">Assumptions!$C$44*(1+A22)</f>
         <v>42.9562547966232</v>
       </c>
       <c r="C22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>-14593.5928779739</v>
       </c>
       <c r="D22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>-11518.6536914812</v>
       </c>
       <c r="E22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>-8443.71450498848</v>
       </c>
       <c r="F22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>-5368.77531849578</v>
       </c>
       <c r="G22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>-2293.83613200307</v>
       </c>
       <c r="H22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>781.103054489635</v>
       </c>
       <c r="I22" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B22)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B22)-Assumptions!$C$47</f>
         <v>3856.04224098234</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="46" t="n">
-        <f aca="false">A22+Assumptions!$C$60</f>
+        <f aca="false">A22+Assumptions!$C$63</f>
         <v>0.1</v>
       </c>
       <c r="B23" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A23)</f>
+        <f aca="false">Assumptions!$C$44*(1+A23)</f>
         <v>47.2518802762855</v>
       </c>
       <c r="C23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-19713.9784497314</v>
       </c>
       <c r="D23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-16639.0392632387</v>
       </c>
       <c r="E23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-13564.100076746</v>
       </c>
       <c r="F23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-10489.1608902533</v>
       </c>
       <c r="G23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-7414.22170376056</v>
       </c>
       <c r="H23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-4339.28251726785</v>
       </c>
       <c r="I23" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B23)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B23)-Assumptions!$C$47</f>
         <v>-1264.34333077514</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="46" t="n">
-        <f aca="false">A23+Assumptions!$C$60</f>
+        <f aca="false">A23+Assumptions!$C$63</f>
         <v>0.2</v>
       </c>
       <c r="B24" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A24)</f>
+        <f aca="false">Assumptions!$C$44*(1+A24)</f>
         <v>51.5475057559478</v>
       </c>
       <c r="C24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-24834.3640214889</v>
       </c>
       <c r="D24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-21759.4248349962</v>
       </c>
       <c r="E24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-18684.4856485034</v>
       </c>
       <c r="F24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-15609.5464620107</v>
       </c>
       <c r="G24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-12534.607275518</v>
       </c>
       <c r="H24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-9459.66808902533</v>
       </c>
       <c r="I24" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B24)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B24)-Assumptions!$C$47</f>
         <v>-6384.72890253262</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="n">
-        <f aca="false">A24+Assumptions!$C$60</f>
+        <f aca="false">A24+Assumptions!$C$63</f>
         <v>0.3</v>
       </c>
       <c r="B25" s="48" t="n">
-        <f aca="false">Assumptions!$C$41*(1+A25)</f>
+        <f aca="false">Assumptions!$C$44*(1+A25)</f>
         <v>55.8431312356101</v>
       </c>
       <c r="C25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*C$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*C$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-29954.7495932463</v>
       </c>
       <c r="D25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*D$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*D$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-26879.8104067536</v>
       </c>
       <c r="E25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*E$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*E$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-23804.8712202609</v>
       </c>
       <c r="F25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*F$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*F$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-20729.9320337682</v>
       </c>
       <c r="G25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*G$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*G$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-17654.9928472755</v>
       </c>
       <c r="H25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*H$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*H$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-14580.0536607828</v>
       </c>
       <c r="I25" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*I$18+Assumptions!$C$64-$B25)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*I$18+Assumptions!$C$67-$B25)-Assumptions!$C$47</f>
         <v>-11505.1144742901</v>
       </c>
     </row>
@@ -4635,65 +5371,65 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>251</v>
+        <v>301</v>
       </c>
       <c r="B4" s="50" t="n">
-        <f aca="false">Assumptions!$C$61</f>
+        <f aca="false">Assumptions!$C$64</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="B5" s="51" t="n">
-        <f aca="false">Assumptions!$C$68</f>
+        <f aca="false">Assumptions!$C$71</f>
         <v>-8443.71450498848</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="G7" s="40" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="B8" s="52" t="n">
         <f aca="false">B$4</f>
         <v>0.1</v>
       </c>
       <c r="C8" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*Assumptions!$C$9*(1+B8)+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*Assumptions!$C$9*(1+B8)+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-2293.83613200307</v>
       </c>
       <c r="D8" s="38" t="n">
@@ -4715,14 +5451,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="B9" s="52" t="n">
         <f aca="false">B$4</f>
         <v>0.1</v>
       </c>
       <c r="C9" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(1+B9)*(Assumptions!$C$63*Assumptions!$C$9+Assumptions!$C$64-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(1+B9)*(Assumptions!$C$66*Assumptions!$C$9+Assumptions!$C$67-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-6087.8449731389</v>
       </c>
       <c r="D9" s="38" t="n">
@@ -4744,14 +5480,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="B10" s="52" t="n">
         <f aca="false">-B$4</f>
         <v>-0.1</v>
       </c>
       <c r="C10" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*Assumptions!$C$9+Assumptions!$C$64-Assumptions!$C$41*(1+B10))-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*Assumptions!$C$9+Assumptions!$C$67-Assumptions!$C$44*(1+B10))-Assumptions!$C$47</f>
         <v>-3323.32893323101</v>
       </c>
       <c r="D10" s="38" t="n">
@@ -4773,14 +5509,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="B11" s="52" t="n">
         <f aca="false">B$4</f>
         <v>0.1</v>
       </c>
       <c r="C11" s="38" t="n">
-        <f aca="false">Assumptions!$C$10*(Assumptions!$C$63*Assumptions!$C$9+Assumptions!$C$64+Assumptions!$C$38*B11-Assumptions!$C$41)-Assumptions!$C$44</f>
+        <f aca="false">Assumptions!$C$10*(Assumptions!$C$66*Assumptions!$C$9+Assumptions!$C$67+Assumptions!$C$41*B11-Assumptions!$C$44)-Assumptions!$C$47</f>
         <v>-6052.39600920951</v>
       </c>
       <c r="D11" s="38" t="n">
@@ -4802,21 +5538,21 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4900,4 +5636,1337 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:P45"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="3" style="0" width="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="55" t="str">
+        <f aca="false">"Range (modeled): all three fixes together improve store contribution by "&amp;TEXT(B21,"#,##0")&amp;" to "&amp;TEXT(D21,"#,##0")&amp;" INR per store per month (central "&amp;TEXT(C21,"#,##0")&amp;"). Across "&amp;TEXT(B13,"#,##0")&amp;" stores that is "&amp;TEXT(E21,"0.0")&amp;" to "&amp;TEXT(G21,"0.0")&amp;" INR crore per month (central "&amp;TEXT(F21,"0.0")&amp;"), or "&amp;TEXT(H21,"0")&amp;" to "&amp;TEXT(J21,"0")&amp;" INR crore per year."</f>
+        <v>Range (modeled): all three fixes together improve store contribution by 122,470 to 502,803 INR per store per month (central 254,935). Across 1,240 stores that is 15.2 to 62.3 INR crore per month (central 31.6), or 182 to 748 INR crore per year.</v>
+      </c>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="55" t="str">
+        <f aca="false">"Base case: each store loses about "&amp;TEXT(-B23,"#,##0")&amp;" INR per month, or "&amp;TEXT(-B24,"0.0")&amp;" INR crore per month across the same stores."</f>
+        <v>Base case: each store loses about 253,311 INR per month, or 31.4 INR crore per month across the same stores.</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B9" s="56" t="n">
+        <f aca="false">Assumptions!$C$73</f>
+        <v>0.02</v>
+      </c>
+      <c r="C9" s="56" t="n">
+        <f aca="false">Assumptions!$C$74</f>
+        <v>0.043</v>
+      </c>
+      <c r="D9" s="56" t="n">
+        <f aca="false">Assumptions!$C$75</f>
+        <v>0.08</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" s="56" t="n">
+        <f aca="false">Assumptions!$C$76</f>
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="56" t="n">
+        <f aca="false">Assumptions!$C$77</f>
+        <v>0.095</v>
+      </c>
+      <c r="D10" s="56" t="n">
+        <f aca="false">Assumptions!$C$78</f>
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B11" s="56" t="n">
+        <f aca="false">Assumptions!$C$79</f>
+        <v>-0.03</v>
+      </c>
+      <c r="C11" s="56" t="n">
+        <f aca="false">Assumptions!$C$80</f>
+        <v>-0.06</v>
+      </c>
+      <c r="D11" s="56" t="n">
+        <f aca="false">Assumptions!$C$81</f>
+        <v>-0.1</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="51" t="n">
+        <f aca="false">Assumptions!$C$83</f>
+        <v>1240</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="51" t="n">
+        <f aca="false">Assumptions!$C$33</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>332</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="I17" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="J17" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="K17" s="40" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B18" s="38" t="n">
+        <f aca="false">M28</f>
+        <v>36899.2702379125</v>
+      </c>
+      <c r="C18" s="38" t="n">
+        <f aca="false">M29</f>
+        <v>79333.4310115115</v>
+      </c>
+      <c r="D18" s="38" t="n">
+        <f aca="false">M30</f>
+        <v>147597.08095165</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <f aca="false">N28</f>
+        <v>4.57550950950115</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <f aca="false">N29</f>
+        <v>9.83734544542742</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <f aca="false">N30</f>
+        <v>18.3020380380046</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <f aca="false">O28</f>
+        <v>54.9061141140139</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <f aca="false">O29</f>
+        <v>118.048145345129</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <f aca="false">O30</f>
+        <v>219.624456456055</v>
+      </c>
+      <c r="K18" s="57" t="str">
+        <f aca="false">P29</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B19" s="38" t="n">
+        <f aca="false">M31</f>
+        <v>35338.0429777438</v>
+      </c>
+      <c r="C19" s="38" t="n">
+        <f aca="false">M32</f>
+        <v>67142.281657713</v>
+      </c>
+      <c r="D19" s="38" t="n">
+        <f aca="false">M33</f>
+        <v>141352.171910975</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <f aca="false">N31</f>
+        <v>4.38191732924023</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <f aca="false">N32</f>
+        <v>8.32564292555642</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <f aca="false">N33</f>
+        <v>17.5276693169609</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <f aca="false">O31</f>
+        <v>52.5830079508828</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <f aca="false">O32</f>
+        <v>99.907715106677</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <f aca="false">O33</f>
+        <v>210.33203180353</v>
+      </c>
+      <c r="K19" s="57" t="str">
+        <f aca="false">P32</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" s="38" t="n">
+        <f aca="false">M34</f>
+        <v>46083.4701458174</v>
+      </c>
+      <c r="C20" s="38" t="n">
+        <f aca="false">M35</f>
+        <v>92166.9402916349</v>
+      </c>
+      <c r="D20" s="38" t="n">
+        <f aca="false">M36</f>
+        <v>153611.567152724</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <f aca="false">N34</f>
+        <v>5.71435029808136</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <f aca="false">N35</f>
+        <v>11.4287005961627</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <f aca="false">N36</f>
+        <v>19.0478343269378</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <f aca="false">O34</f>
+        <v>68.5722035769763</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <f aca="false">O35</f>
+        <v>137.144407153953</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <f aca="false">O36</f>
+        <v>228.574011923254</v>
+      </c>
+      <c r="K20" s="57" t="str">
+        <f aca="false">P35</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" s="58" t="n">
+        <f aca="false">M37</f>
+        <v>122469.92038066</v>
+      </c>
+      <c r="C21" s="58" t="n">
+        <f aca="false">M38</f>
+        <v>254935.188234658</v>
+      </c>
+      <c r="D21" s="58" t="n">
+        <f aca="false">M39</f>
+        <v>502802.549636224</v>
+      </c>
+      <c r="E21" s="59" t="n">
+        <f aca="false">N37</f>
+        <v>15.1862701272019</v>
+      </c>
+      <c r="F21" s="59" t="n">
+        <f aca="false">N38</f>
+        <v>31.6119633410976</v>
+      </c>
+      <c r="G21" s="59" t="n">
+        <f aca="false">N39</f>
+        <v>62.3475161548917</v>
+      </c>
+      <c r="H21" s="59" t="n">
+        <f aca="false">O37</f>
+        <v>182.235241526422</v>
+      </c>
+      <c r="I21" s="59" t="n">
+        <f aca="false">O38</f>
+        <v>379.343560093171</v>
+      </c>
+      <c r="J21" s="59" t="n">
+        <f aca="false">O39</f>
+        <v>748.170193858701</v>
+      </c>
+      <c r="K21" s="60" t="str">
+        <f aca="false">P38</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B23" s="38" t="n">
+        <f aca="false">L27</f>
+        <v>-253311.435149654</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="B24" s="30" t="n">
+        <f aca="false">B23*B13/Assumptions!$C$85</f>
+        <v>-31.4106179585572</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="J26" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="K26" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="L26" s="40" t="s">
+        <v>352</v>
+      </c>
+      <c r="M26" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="N26" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="O26" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="P26" s="40" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C27" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D27)</f>
+        <v>1192</v>
+      </c>
+      <c r="G27" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C27)</f>
+        <v>506</v>
+      </c>
+      <c r="H27" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E27)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I27" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G27+Assumptions!$C$67-H27</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <f aca="false">I27-Assumptions!$C$47/F27</f>
+        <v>-7.08365310821181</v>
+      </c>
+      <c r="K27" s="38" t="n">
+        <f aca="false">F27*I27-Assumptions!$C$47</f>
+        <v>-8443.71450498848</v>
+      </c>
+      <c r="L27" s="38" t="n">
+        <f aca="false">K27*$B$14</f>
+        <v>-253311.435149654</v>
+      </c>
+      <c r="M27" s="38" t="n">
+        <f aca="false">L27-$L$27</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="30" t="n">
+        <f aca="false">M27*$B$13/Assumptions!$C$85</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="30" t="n">
+        <f aca="false">N27*Assumptions!$C$84</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="57" t="str">
+        <f aca="false">IF(K27&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C28" s="61" t="n">
+        <f aca="false">B$9</f>
+        <v>0.02</v>
+      </c>
+      <c r="D28" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D28)</f>
+        <v>1192</v>
+      </c>
+      <c r="G28" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C28)</f>
+        <v>516.12</v>
+      </c>
+      <c r="H28" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E28)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I28" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G28+Assumptions!$C$67-H28</f>
+        <v>20.7958649270913</v>
+      </c>
+      <c r="J28" s="30" t="n">
+        <f aca="false">I28-Assumptions!$C$47/F28</f>
+        <v>-6.05179432079815</v>
+      </c>
+      <c r="K28" s="38" t="n">
+        <f aca="false">F28*I28-Assumptions!$C$47</f>
+        <v>-7213.7388303914</v>
+      </c>
+      <c r="L28" s="38" t="n">
+        <f aca="false">K28*$B$14</f>
+        <v>-216412.164911742</v>
+      </c>
+      <c r="M28" s="38" t="n">
+        <f aca="false">L28-$L$27</f>
+        <v>36899.2702379125</v>
+      </c>
+      <c r="N28" s="30" t="n">
+        <f aca="false">M28*$B$13/Assumptions!$C$85</f>
+        <v>4.57550950950115</v>
+      </c>
+      <c r="O28" s="30" t="n">
+        <f aca="false">N28*Assumptions!$C$84</f>
+        <v>54.9061141140139</v>
+      </c>
+      <c r="P28" s="57" t="str">
+        <f aca="false">IF(K28&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" s="61" t="n">
+        <f aca="false">C$9</f>
+        <v>0.043</v>
+      </c>
+      <c r="D29" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D29)</f>
+        <v>1192</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C29)</f>
+        <v>527.758</v>
+      </c>
+      <c r="H29" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E29)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I29" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G29+Assumptions!$C$67-H29</f>
+        <v>21.982502532617</v>
+      </c>
+      <c r="J29" s="30" t="n">
+        <f aca="false">I29-Assumptions!$C$47/F29</f>
+        <v>-4.86515671527246</v>
+      </c>
+      <c r="K29" s="38" t="n">
+        <f aca="false">F29*I29-Assumptions!$C$47</f>
+        <v>-5799.26680460477</v>
+      </c>
+      <c r="L29" s="38" t="n">
+        <f aca="false">K29*$B$14</f>
+        <v>-173978.004138143</v>
+      </c>
+      <c r="M29" s="38" t="n">
+        <f aca="false">L29-$L$27</f>
+        <v>79333.4310115115</v>
+      </c>
+      <c r="N29" s="30" t="n">
+        <f aca="false">M29*$B$13/Assumptions!$C$85</f>
+        <v>9.83734544542742</v>
+      </c>
+      <c r="O29" s="30" t="n">
+        <f aca="false">N29*Assumptions!$C$84</f>
+        <v>118.048145345129</v>
+      </c>
+      <c r="P29" s="57" t="str">
+        <f aca="false">IF(K29&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C30" s="61" t="n">
+        <f aca="false">D$9</f>
+        <v>0.08</v>
+      </c>
+      <c r="D30" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D30)</f>
+        <v>1192</v>
+      </c>
+      <c r="G30" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C30)</f>
+        <v>546.48</v>
+      </c>
+      <c r="H30" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E30)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I30" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G30+Assumptions!$C$67-H30</f>
+        <v>23.8914412893323</v>
+      </c>
+      <c r="J30" s="30" t="n">
+        <f aca="false">I30-Assumptions!$C$47/F30</f>
+        <v>-2.95621795855717</v>
+      </c>
+      <c r="K30" s="38" t="n">
+        <f aca="false">F30*I30-Assumptions!$C$47</f>
+        <v>-3523.81180660014</v>
+      </c>
+      <c r="L30" s="38" t="n">
+        <f aca="false">K30*$B$14</f>
+        <v>-105714.354198004</v>
+      </c>
+      <c r="M30" s="38" t="n">
+        <f aca="false">L30-$L$27</f>
+        <v>147597.08095165</v>
+      </c>
+      <c r="N30" s="30" t="n">
+        <f aca="false">M30*$B$13/Assumptions!$C$85</f>
+        <v>18.3020380380046</v>
+      </c>
+      <c r="O30" s="30" t="n">
+        <f aca="false">N30*Assumptions!$C$84</f>
+        <v>219.624456456055</v>
+      </c>
+      <c r="P30" s="57" t="str">
+        <f aca="false">IF(K30&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="61" t="n">
+        <f aca="false">B$10</f>
+        <v>0.05</v>
+      </c>
+      <c r="E31" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D31)</f>
+        <v>1251.6</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C31)</f>
+        <v>506</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E31)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I31" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G31+Assumptions!$C$67-H31</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="J31" s="30" t="n">
+        <f aca="false">I31-Assumptions!$C$47/F31</f>
+        <v>-5.8051931440266</v>
+      </c>
+      <c r="K31" s="38" t="n">
+        <f aca="false">F31*I31-Assumptions!$C$47</f>
+        <v>-7265.77973906369</v>
+      </c>
+      <c r="L31" s="38" t="n">
+        <f aca="false">K31*$B$14</f>
+        <v>-217973.392171911</v>
+      </c>
+      <c r="M31" s="38" t="n">
+        <f aca="false">L31-$L$27</f>
+        <v>35338.0429777438</v>
+      </c>
+      <c r="N31" s="30" t="n">
+        <f aca="false">M31*$B$13/Assumptions!$C$85</f>
+        <v>4.38191732924023</v>
+      </c>
+      <c r="O31" s="30" t="n">
+        <f aca="false">N31*Assumptions!$C$84</f>
+        <v>52.5830079508828</v>
+      </c>
+      <c r="P31" s="57" t="str">
+        <f aca="false">IF(K31&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="61" t="n">
+        <f aca="false">C$10</f>
+        <v>0.095</v>
+      </c>
+      <c r="E32" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D32)</f>
+        <v>1305.24</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C32)</f>
+        <v>506</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E32)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I32" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G32+Assumptions!$C$67-H32</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="J32" s="30" t="n">
+        <f aca="false">I32-Assumptions!$C$47/F32</f>
+        <v>-4.75440413236752</v>
+      </c>
+      <c r="K32" s="38" t="n">
+        <f aca="false">F32*I32-Assumptions!$C$47</f>
+        <v>-6205.63844973138</v>
+      </c>
+      <c r="L32" s="38" t="n">
+        <f aca="false">K32*$B$14</f>
+        <v>-186169.153491941</v>
+      </c>
+      <c r="M32" s="38" t="n">
+        <f aca="false">L32-$L$27</f>
+        <v>67142.281657713</v>
+      </c>
+      <c r="N32" s="30" t="n">
+        <f aca="false">M32*$B$13/Assumptions!$C$85</f>
+        <v>8.32564292555642</v>
+      </c>
+      <c r="O32" s="30" t="n">
+        <f aca="false">N32*Assumptions!$C$84</f>
+        <v>99.907715106677</v>
+      </c>
+      <c r="P32" s="57" t="str">
+        <f aca="false">IF(K32&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C33" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="61" t="n">
+        <f aca="false">D$10</f>
+        <v>0.2</v>
+      </c>
+      <c r="E33" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D33)</f>
+        <v>1430.4</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C33)</f>
+        <v>506</v>
+      </c>
+      <c r="H33" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E33)</f>
+        <v>42.9562547966232</v>
+      </c>
+      <c r="I33" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G33+Assumptions!$C$67-H33</f>
+        <v>19.7640061396777</v>
+      </c>
+      <c r="J33" s="30" t="n">
+        <f aca="false">I33-Assumptions!$C$47/F33</f>
+        <v>-2.60904323356357</v>
+      </c>
+      <c r="K33" s="38" t="n">
+        <f aca="false">F33*I33-Assumptions!$C$47</f>
+        <v>-3731.97544128933</v>
+      </c>
+      <c r="L33" s="38" t="n">
+        <f aca="false">K33*$B$14</f>
+        <v>-111959.26323868</v>
+      </c>
+      <c r="M33" s="38" t="n">
+        <f aca="false">L33-$L$27</f>
+        <v>141352.171910975</v>
+      </c>
+      <c r="N33" s="30" t="n">
+        <f aca="false">M33*$B$13/Assumptions!$C$85</f>
+        <v>17.5276693169609</v>
+      </c>
+      <c r="O33" s="30" t="n">
+        <f aca="false">N33*Assumptions!$C$84</f>
+        <v>210.33203180353</v>
+      </c>
+      <c r="P33" s="57" t="str">
+        <f aca="false">IF(K33&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C34" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="61" t="n">
+        <f aca="false">B$11</f>
+        <v>-0.03</v>
+      </c>
+      <c r="F34" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D34)</f>
+        <v>1192</v>
+      </c>
+      <c r="G34" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C34)</f>
+        <v>506</v>
+      </c>
+      <c r="H34" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E34)</f>
+        <v>41.6675671527245</v>
+      </c>
+      <c r="I34" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G34+Assumptions!$C$67-H34</f>
+        <v>21.0526937835764</v>
+      </c>
+      <c r="J34" s="30" t="n">
+        <f aca="false">I34-Assumptions!$C$47/F34</f>
+        <v>-5.79496546431312</v>
+      </c>
+      <c r="K34" s="38" t="n">
+        <f aca="false">F34*I34-Assumptions!$C$47</f>
+        <v>-6907.59883346123</v>
+      </c>
+      <c r="L34" s="38" t="n">
+        <f aca="false">K34*$B$14</f>
+        <v>-207227.965003837</v>
+      </c>
+      <c r="M34" s="38" t="n">
+        <f aca="false">L34-$L$27</f>
+        <v>46083.4701458174</v>
+      </c>
+      <c r="N34" s="30" t="n">
+        <f aca="false">M34*$B$13/Assumptions!$C$85</f>
+        <v>5.71435029808136</v>
+      </c>
+      <c r="O34" s="30" t="n">
+        <f aca="false">N34*Assumptions!$C$84</f>
+        <v>68.5722035769763</v>
+      </c>
+      <c r="P34" s="57" t="str">
+        <f aca="false">IF(K34&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C35" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="61" t="n">
+        <f aca="false">C$11</f>
+        <v>-0.06</v>
+      </c>
+      <c r="F35" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D35)</f>
+        <v>1192</v>
+      </c>
+      <c r="G35" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C35)</f>
+        <v>506</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E35)</f>
+        <v>40.3788795088258</v>
+      </c>
+      <c r="I35" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G35+Assumptions!$C$67-H35</f>
+        <v>22.3413814274751</v>
+      </c>
+      <c r="J35" s="30" t="n">
+        <f aca="false">I35-Assumptions!$C$47/F35</f>
+        <v>-4.50627782041442</v>
+      </c>
+      <c r="K35" s="38" t="n">
+        <f aca="false">F35*I35-Assumptions!$C$47</f>
+        <v>-5371.48316193399</v>
+      </c>
+      <c r="L35" s="38" t="n">
+        <f aca="false">K35*$B$14</f>
+        <v>-161144.49485802</v>
+      </c>
+      <c r="M35" s="38" t="n">
+        <f aca="false">L35-$L$27</f>
+        <v>92166.9402916349</v>
+      </c>
+      <c r="N35" s="30" t="n">
+        <f aca="false">M35*$B$13/Assumptions!$C$85</f>
+        <v>11.4287005961627</v>
+      </c>
+      <c r="O35" s="30" t="n">
+        <f aca="false">N35*Assumptions!$C$84</f>
+        <v>137.144407153953</v>
+      </c>
+      <c r="P35" s="57" t="str">
+        <f aca="false">IF(K35&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C36" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="61" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="61" t="n">
+        <f aca="false">D$11</f>
+        <v>-0.1</v>
+      </c>
+      <c r="F36" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D36)</f>
+        <v>1192</v>
+      </c>
+      <c r="G36" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C36)</f>
+        <v>506</v>
+      </c>
+      <c r="H36" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E36)</f>
+        <v>38.6606293169609</v>
+      </c>
+      <c r="I36" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G36+Assumptions!$C$67-H36</f>
+        <v>24.05963161934</v>
+      </c>
+      <c r="J36" s="30" t="n">
+        <f aca="false">I36-Assumptions!$C$47/F36</f>
+        <v>-2.7880276285495</v>
+      </c>
+      <c r="K36" s="38" t="n">
+        <f aca="false">F36*I36-Assumptions!$C$47</f>
+        <v>-3323.32893323101</v>
+      </c>
+      <c r="L36" s="38" t="n">
+        <f aca="false">K36*$B$14</f>
+        <v>-99699.8679969301</v>
+      </c>
+      <c r="M36" s="38" t="n">
+        <f aca="false">L36-$L$27</f>
+        <v>153611.567152724</v>
+      </c>
+      <c r="N36" s="30" t="n">
+        <f aca="false">M36*$B$13/Assumptions!$C$85</f>
+        <v>19.0478343269378</v>
+      </c>
+      <c r="O36" s="30" t="n">
+        <f aca="false">N36*Assumptions!$C$84</f>
+        <v>228.574011923254</v>
+      </c>
+      <c r="P36" s="57" t="str">
+        <f aca="false">IF(K36&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" s="61" t="n">
+        <f aca="false">B$9</f>
+        <v>0.02</v>
+      </c>
+      <c r="D37" s="61" t="n">
+        <f aca="false">B$10</f>
+        <v>0.05</v>
+      </c>
+      <c r="E37" s="61" t="n">
+        <f aca="false">B$11</f>
+        <v>-0.03</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D37)</f>
+        <v>1251.6</v>
+      </c>
+      <c r="G37" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C37)</f>
+        <v>516.12</v>
+      </c>
+      <c r="H37" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E37)</f>
+        <v>41.6675671527245</v>
+      </c>
+      <c r="I37" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G37+Assumptions!$C$67-H37</f>
+        <v>22.08455257099</v>
+      </c>
+      <c r="J37" s="30" t="n">
+        <f aca="false">I37-Assumptions!$C$47/F37</f>
+        <v>-3.48464671271424</v>
+      </c>
+      <c r="K37" s="38" t="n">
+        <f aca="false">F37*I37-Assumptions!$C$47</f>
+        <v>-4361.38382563314</v>
+      </c>
+      <c r="L37" s="38" t="n">
+        <f aca="false">K37*$B$14</f>
+        <v>-130841.514768994</v>
+      </c>
+      <c r="M37" s="38" t="n">
+        <f aca="false">L37-$L$27</f>
+        <v>122469.92038066</v>
+      </c>
+      <c r="N37" s="30" t="n">
+        <f aca="false">M37*$B$13/Assumptions!$C$85</f>
+        <v>15.1862701272019</v>
+      </c>
+      <c r="O37" s="30" t="n">
+        <f aca="false">N37*Assumptions!$C$84</f>
+        <v>182.235241526422</v>
+      </c>
+      <c r="P37" s="57" t="str">
+        <f aca="false">IF(K37&gt;=0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C38" s="61" t="n">
+        <f aca="false">C$9</f>
+        <v>0.043</v>
+      </c>
+      <c r="D38" s="61" t="n">
+        <f aca="false">C$10</f>
+        <v>0.095</v>
+      </c>
+      <c r="E38" s="61" t="n">
+        <f aca="false">C$11</f>
+        <v>-0.06</v>
+      </c>
+      <c r="F38" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D38)</f>
+        <v>1305.24</v>
+      </c>
+      <c r="G38" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C38)</f>
+        <v>527.758</v>
+      </c>
+      <c r="H38" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E38)</f>
+        <v>40.3788795088258</v>
+      </c>
+      <c r="I38" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G38+Assumptions!$C$67-H38</f>
+        <v>24.5598778204144</v>
+      </c>
+      <c r="J38" s="30" t="n">
+        <f aca="false">I38-Assumptions!$C$47/F38</f>
+        <v>0.0414675483692335</v>
+      </c>
+      <c r="K38" s="38" t="n">
+        <f aca="false">F38*I38-Assumptions!$C$47</f>
+        <v>54.1251028334555</v>
+      </c>
+      <c r="L38" s="38" t="n">
+        <f aca="false">K38*$B$14</f>
+        <v>1623.75308500366</v>
+      </c>
+      <c r="M38" s="38" t="n">
+        <f aca="false">L38-$L$27</f>
+        <v>254935.188234658</v>
+      </c>
+      <c r="N38" s="30" t="n">
+        <f aca="false">M38*$B$13/Assumptions!$C$85</f>
+        <v>31.6119633410976</v>
+      </c>
+      <c r="O38" s="30" t="n">
+        <f aca="false">N38*Assumptions!$C$84</f>
+        <v>379.343560093171</v>
+      </c>
+      <c r="P38" s="57" t="str">
+        <f aca="false">IF(K38&gt;=0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C39" s="61" t="n">
+        <f aca="false">D$9</f>
+        <v>0.08</v>
+      </c>
+      <c r="D39" s="61" t="n">
+        <f aca="false">D$10</f>
+        <v>0.2</v>
+      </c>
+      <c r="E39" s="61" t="n">
+        <f aca="false">D$11</f>
+        <v>-0.1</v>
+      </c>
+      <c r="F39" s="38" t="n">
+        <f aca="false">Assumptions!$C$10*(1+D39)</f>
+        <v>1430.4</v>
+      </c>
+      <c r="G39" s="30" t="n">
+        <f aca="false">Assumptions!$C$9*(1+C39)</f>
+        <v>546.48</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <f aca="false">Assumptions!$C$44*(1+E39)</f>
+        <v>38.6606293169609</v>
+      </c>
+      <c r="I39" s="30" t="n">
+        <f aca="false">Assumptions!$C$66*G39+Assumptions!$C$67-H39</f>
+        <v>28.1870667689946</v>
+      </c>
+      <c r="J39" s="30" t="n">
+        <f aca="false">I39-Assumptions!$C$47/F39</f>
+        <v>5.81401739575339</v>
+      </c>
+      <c r="K39" s="38" t="n">
+        <f aca="false">F39*I39-Assumptions!$C$47</f>
+        <v>8316.37048288564</v>
+      </c>
+      <c r="L39" s="38" t="n">
+        <f aca="false">K39*$B$14</f>
+        <v>249491.114486569</v>
+      </c>
+      <c r="M39" s="38" t="n">
+        <f aca="false">L39-$L$27</f>
+        <v>502802.549636224</v>
+      </c>
+      <c r="N39" s="30" t="n">
+        <f aca="false">M39*$B$13/Assumptions!$C$85</f>
+        <v>62.3475161548917</v>
+      </c>
+      <c r="O39" s="30" t="n">
+        <f aca="false">N39*Assumptions!$C$84</f>
+        <v>748.170193858701</v>
+      </c>
+      <c r="P39" s="57" t="str">
+        <f aca="false">IF(K39&gt;=0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="32" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="32" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="32" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="32" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K27:L39">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>